--- a/config/Excel/NPC.xlsx
+++ b/config/Excel/NPC.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC" sheetId="1" r:id="R52e87017cff040a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC" sheetId="1" r:id="R68ea60a2b86e4c8d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -153,17 +153,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NPCTable" displayName="NPCTable" ref="A1:I9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="9">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NPCTable" displayName="NPCTable" ref="A1:G81" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="7">
     <x:tableColumn id="1" name="NPC識別碼"/>
     <x:tableColumn id="2" name="NPC名稱"/>
-    <x:tableColumn id="3" name="屬性"/>
-    <x:tableColumn id="4" name="外觀"/>
-    <x:tableColumn id="5" name="魔法型（1是／0否）"/>
-    <x:tableColumn id="6" name="生命倍率"/>
-    <x:tableColumn id="7" name="攻擊倍率"/>
-    <x:tableColumn id="8" name="防禦倍率"/>
-    <x:tableColumn id="9" name="攻速倍率"/>
+    <x:tableColumn id="3" name="所屬地圖識別碼"/>
+    <x:tableColumn id="4" name="屬性"/>
+    <x:tableColumn id="5" name="外觀"/>
+    <x:tableColumn id="6" name="魔法型（1是／0否）"/>
+    <x:tableColumn id="7" name="出現權重"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -366,13 +364,11 @@
   <x:cols>
     <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -383,263 +379,1865 @@
         <x:v>NPC名稱</x:v>
       </x:c>
       <x:c r="C1" s="14" t="str">
+        <x:v>所屬地圖識別碼</x:v>
+      </x:c>
+      <x:c r="D1" s="14" t="str">
         <x:v>屬性</x:v>
       </x:c>
-      <x:c r="D1" s="14" t="str">
+      <x:c r="E1" s="14" t="str">
         <x:v>外觀</x:v>
       </x:c>
-      <x:c r="E1" s="14" t="str">
+      <x:c r="F1" s="14" t="str">
         <x:v>魔法型（1是／0否）</x:v>
       </x:c>
-      <x:c r="F1" s="14" t="str">
-        <x:v>生命倍率</x:v>
-      </x:c>
       <x:c r="G1" s="14" t="str">
-        <x:v>攻擊倍率</x:v>
-      </x:c>
-      <x:c r="H1" s="14" t="str">
-        <x:v>防禦倍率</x:v>
-      </x:c>
-      <x:c r="I1" s="14" t="str">
-        <x:v>攻速倍率</x:v>
+        <x:v>出現權重</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="18" t="str">
-        <x:v>undead_skeleton</x:v>
+        <x:v>plains_1</x:v>
       </x:c>
       <x:c r="B2" s="18" t="str">
-        <x:v>骸骨戰士</x:v>
+        <x:v>史萊姆</x:v>
       </x:c>
       <x:c r="C2" s="18" t="str">
-        <x:v>dark</x:v>
+        <x:v>plains</x:v>
       </x:c>
       <x:c r="D2" s="18" t="str">
-        <x:v>skeleton</x:v>
-      </x:c>
-      <x:c r="E2" s="20" t="str">
-        <x:v>0</x:v>
+        <x:v>poison</x:v>
+      </x:c>
+      <x:c r="E2" s="18" t="str">
+        <x:v>🟢</x:v>
       </x:c>
       <x:c r="F2" s="20" t="str">
-        <x:v>1.05</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2" s="20" t="str">
-        <x:v>1.1</x:v>
-      </x:c>
-      <x:c r="H2" s="20" t="str">
-        <x:v>1.2</x:v>
-      </x:c>
-      <x:c r="I2" s="20" t="str">
-        <x:v>1</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="18" t="str">
-        <x:v>undead_wraith</x:v>
+        <x:v>plains_2</x:v>
       </x:c>
       <x:c r="B3" s="18" t="str">
-        <x:v>山脈怨靈</x:v>
+        <x:v>哥布林</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
+        <x:v>plains</x:v>
+      </x:c>
+      <x:c r="D3" s="18" t="str">
         <x:v>dark</x:v>
       </x:c>
-      <x:c r="D3" s="18" t="str">
-        <x:v>wraith</x:v>
-      </x:c>
-      <x:c r="E3" s="20" t="str">
-        <x:v>1</x:v>
+      <x:c r="E3" s="18" t="str">
+        <x:v>👺</x:v>
       </x:c>
       <x:c r="F3" s="20" t="str">
-        <x:v>0.85</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3" s="20" t="str">
-        <x:v>1.25</x:v>
-      </x:c>
-      <x:c r="H3" s="20" t="str">
-        <x:v>0.9</x:v>
-      </x:c>
-      <x:c r="I3" s="20" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="18" t="str">
-        <x:v>undead_ghoul</x:v>
+        <x:v>plains_3</x:v>
       </x:c>
       <x:c r="B4" s="18" t="str">
-        <x:v>腐屍獵犬</x:v>
+        <x:v>野狼</x:v>
       </x:c>
       <x:c r="C4" s="18" t="str">
-        <x:v>poison</x:v>
+        <x:v>plains</x:v>
       </x:c>
       <x:c r="D4" s="18" t="str">
-        <x:v>ghoul</x:v>
-      </x:c>
-      <x:c r="E4" s="20" t="str">
-        <x:v>0</x:v>
+        <x:v>ice</x:v>
+      </x:c>
+      <x:c r="E4" s="18" t="str">
+        <x:v>🐺</x:v>
       </x:c>
       <x:c r="F4" s="20" t="str">
-        <x:v>0.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G4" s="20" t="str">
-        <x:v>1.2</x:v>
-      </x:c>
-      <x:c r="H4" s="20" t="str">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="I4" s="20" t="str">
-        <x:v>1.2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="18" t="str">
-        <x:v>undead_knight</x:v>
+        <x:v>plains_4</x:v>
       </x:c>
       <x:c r="B5" s="18" t="str">
-        <x:v>亡靈騎士</x:v>
+        <x:v>骷髏兵</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
+        <x:v>plains</x:v>
+      </x:c>
+      <x:c r="D5" s="18" t="str">
         <x:v>dark</x:v>
       </x:c>
-      <x:c r="D5" s="18" t="str">
-        <x:v>knight</x:v>
-      </x:c>
-      <x:c r="E5" s="20" t="str">
-        <x:v>0</x:v>
+      <x:c r="E5" s="18" t="str">
+        <x:v>💀</x:v>
       </x:c>
       <x:c r="F5" s="20" t="str">
-        <x:v>1.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G5" s="20" t="str">
-        <x:v>1.05</x:v>
-      </x:c>
-      <x:c r="H5" s="20" t="str">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="I5" s="20" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="18" t="str">
-        <x:v>undead_banshee</x:v>
+        <x:v>plains_5</x:v>
       </x:c>
       <x:c r="B6" s="18" t="str">
-        <x:v>哀嚎女妖</x:v>
+        <x:v>暗影蝠</x:v>
       </x:c>
       <x:c r="C6" s="18" t="str">
-        <x:v>ice</x:v>
+        <x:v>plains</x:v>
       </x:c>
       <x:c r="D6" s="18" t="str">
-        <x:v>banshee</x:v>
-      </x:c>
-      <x:c r="E6" s="20" t="str">
-        <x:v>1</x:v>
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E6" s="18" t="str">
+        <x:v>🦇</x:v>
       </x:c>
       <x:c r="F6" s="20" t="str">
-        <x:v>0.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="20" t="str">
-        <x:v>1.35</x:v>
-      </x:c>
-      <x:c r="H6" s="20" t="str">
-        <x:v>0.85</x:v>
-      </x:c>
-      <x:c r="I6" s="20" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="18" t="str">
-        <x:v>undead_golem</x:v>
+        <x:v>plains_6</x:v>
       </x:c>
       <x:c r="B7" s="18" t="str">
-        <x:v>墓石巨像</x:v>
+        <x:v>樹妖</x:v>
       </x:c>
       <x:c r="C7" s="18" t="str">
-        <x:v>earth</x:v>
+        <x:v>plains</x:v>
       </x:c>
       <x:c r="D7" s="18" t="str">
-        <x:v>golem</x:v>
-      </x:c>
-      <x:c r="E7" s="20" t="str">
-        <x:v>0</x:v>
+        <x:v>poison</x:v>
+      </x:c>
+      <x:c r="E7" s="18" t="str">
+        <x:v>🌳</x:v>
       </x:c>
       <x:c r="F7" s="20" t="str">
-        <x:v>1.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="20" t="str">
-        <x:v>0.9</x:v>
-      </x:c>
-      <x:c r="H7" s="20" t="str">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="I7" s="20" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="18" t="str">
-        <x:v>undead_vampire</x:v>
+        <x:v>plains_7</x:v>
       </x:c>
       <x:c r="B8" s="18" t="str">
-        <x:v>血月伯爵</x:v>
+        <x:v>蜥蜴戰士</x:v>
       </x:c>
       <x:c r="C8" s="18" t="str">
-        <x:v>dark</x:v>
+        <x:v>plains</x:v>
       </x:c>
       <x:c r="D8" s="18" t="str">
-        <x:v>vampire</x:v>
-      </x:c>
-      <x:c r="E8" s="20" t="str">
-        <x:v>1</x:v>
+        <x:v>poison</x:v>
+      </x:c>
+      <x:c r="E8" s="18" t="str">
+        <x:v>🦎</x:v>
       </x:c>
       <x:c r="F8" s="20" t="str">
-        <x:v>1.15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G8" s="20" t="str">
-        <x:v>1.4</x:v>
-      </x:c>
-      <x:c r="H8" s="20" t="str">
-        <x:v>1.05</x:v>
-      </x:c>
-      <x:c r="I8" s="20" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="18" t="str">
+        <x:v>plains_8</x:v>
+      </x:c>
+      <x:c r="B9" s="18" t="str">
+        <x:v>半獸人</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="str">
+        <x:v>plains</x:v>
+      </x:c>
+      <x:c r="D9" s="18" t="str">
+        <x:v>fire</x:v>
+      </x:c>
+      <x:c r="E9" s="18" t="str">
+        <x:v>🐗</x:v>
+      </x:c>
+      <x:c r="F9" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="18" t="str">
+        <x:v>plains_9</x:v>
+      </x:c>
+      <x:c r="B10" s="18" t="str">
+        <x:v>幽靈</x:v>
+      </x:c>
+      <x:c r="C10" s="18" t="str">
+        <x:v>plains</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="str">
+        <x:v>👻</x:v>
+      </x:c>
+      <x:c r="F10" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G10" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="18" t="str">
+        <x:v>plains_10</x:v>
+      </x:c>
+      <x:c r="B11" s="18" t="str">
+        <x:v>石像鬼</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="str">
+        <x:v>plains</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="str">
+        <x:v>🗿</x:v>
+      </x:c>
+      <x:c r="F11" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="18" t="str">
+        <x:v>plains_11</x:v>
+      </x:c>
+      <x:c r="B12" s="18" t="str">
+        <x:v>牛頭人</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="str">
+        <x:v>plains</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="str">
+        <x:v>fire</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="str">
+        <x:v>🐂</x:v>
+      </x:c>
+      <x:c r="F12" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="18" t="str">
+        <x:v>plains_12</x:v>
+      </x:c>
+      <x:c r="B13" s="18" t="str">
+        <x:v>雙足飛龍</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="str">
+        <x:v>plains</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="str">
+        <x:v>lightning</x:v>
+      </x:c>
+      <x:c r="E13" s="18" t="str">
+        <x:v>🐉</x:v>
+      </x:c>
+      <x:c r="F13" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="18" t="str">
+        <x:v>desert_1</x:v>
+      </x:c>
+      <x:c r="B14" s="18" t="str">
+        <x:v>沙漠蠍</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="str">
+        <x:v>desert</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="str">
+        <x:v>poison</x:v>
+      </x:c>
+      <x:c r="E14" s="18" t="str">
+        <x:v>🦂</x:v>
+      </x:c>
+      <x:c r="F14" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14" s="20" t="str">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="18" t="str">
+        <x:v>desert_2</x:v>
+      </x:c>
+      <x:c r="B15" s="18" t="str">
+        <x:v>沙蟲</x:v>
+      </x:c>
+      <x:c r="C15" s="18" t="str">
+        <x:v>desert</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="str">
+        <x:v>fire</x:v>
+      </x:c>
+      <x:c r="E15" s="18" t="str">
+        <x:v>🪱</x:v>
+      </x:c>
+      <x:c r="F15" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="18" t="str">
+        <x:v>desert_3</x:v>
+      </x:c>
+      <x:c r="B16" s="18" t="str">
+        <x:v>木乃伊</x:v>
+      </x:c>
+      <x:c r="C16" s="18" t="str">
+        <x:v>desert</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E16" s="18" t="str">
+        <x:v>🧟</x:v>
+      </x:c>
+      <x:c r="F16" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G16" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="18" t="str">
+        <x:v>desert_4</x:v>
+      </x:c>
+      <x:c r="B17" s="18" t="str">
+        <x:v>沙漠禿鷹</x:v>
+      </x:c>
+      <x:c r="C17" s="18" t="str">
+        <x:v>desert</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="str">
+        <x:v>lightning</x:v>
+      </x:c>
+      <x:c r="E17" s="18" t="str">
+        <x:v>🦅</x:v>
+      </x:c>
+      <x:c r="F17" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="18" t="str">
+        <x:v>desert_5</x:v>
+      </x:c>
+      <x:c r="B18" s="18" t="str">
+        <x:v>響尾蛇</x:v>
+      </x:c>
+      <x:c r="C18" s="18" t="str">
+        <x:v>desert</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="str">
+        <x:v>poison</x:v>
+      </x:c>
+      <x:c r="E18" s="18" t="str">
+        <x:v>🐍</x:v>
+      </x:c>
+      <x:c r="F18" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G18" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="18" t="str">
+        <x:v>desert_6</x:v>
+      </x:c>
+      <x:c r="B19" s="18" t="str">
+        <x:v>沙魔</x:v>
+      </x:c>
+      <x:c r="C19" s="18" t="str">
+        <x:v>desert</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E19" s="18" t="str">
+        <x:v>👹</x:v>
+      </x:c>
+      <x:c r="F19" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G19" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="18" t="str">
+        <x:v>desert_7</x:v>
+      </x:c>
+      <x:c r="B20" s="18" t="str">
+        <x:v>石化蜥蜴</x:v>
+      </x:c>
+      <x:c r="C20" s="18" t="str">
+        <x:v>desert</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="str">
+        <x:v>poison</x:v>
+      </x:c>
+      <x:c r="E20" s="18" t="str">
+        <x:v>🦎</x:v>
+      </x:c>
+      <x:c r="F20" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G20" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="18" t="str">
+        <x:v>desert_8</x:v>
+      </x:c>
+      <x:c r="B21" s="18" t="str">
+        <x:v>沙漠強盜</x:v>
+      </x:c>
+      <x:c r="C21" s="18" t="str">
+        <x:v>desert</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="str">
+        <x:v>fire</x:v>
+      </x:c>
+      <x:c r="E21" s="18" t="str">
+        <x:v>🏴‍☠️</x:v>
+      </x:c>
+      <x:c r="F21" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G21" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" s="18" t="str">
+        <x:v>desert_9</x:v>
+      </x:c>
+      <x:c r="B22" s="18" t="str">
+        <x:v>火焰精靈</x:v>
+      </x:c>
+      <x:c r="C22" s="18" t="str">
+        <x:v>desert</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="str">
+        <x:v>fire</x:v>
+      </x:c>
+      <x:c r="E22" s="18" t="str">
+        <x:v>🔥</x:v>
+      </x:c>
+      <x:c r="F22" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G22" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
+      <x:c r="A23" s="18" t="str">
+        <x:v>desert_10</x:v>
+      </x:c>
+      <x:c r="B23" s="18" t="str">
+        <x:v>遠古石像</x:v>
+      </x:c>
+      <x:c r="C23" s="18" t="str">
+        <x:v>desert</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E23" s="18" t="str">
+        <x:v>🗿</x:v>
+      </x:c>
+      <x:c r="F23" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G23" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" s="18" t="str">
+        <x:v>desert_11</x:v>
+      </x:c>
+      <x:c r="B24" s="18" t="str">
+        <x:v>沙丘巨獸</x:v>
+      </x:c>
+      <x:c r="C24" s="18" t="str">
+        <x:v>desert</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="str">
+        <x:v>fire</x:v>
+      </x:c>
+      <x:c r="E24" s="18" t="str">
+        <x:v>🐫</x:v>
+      </x:c>
+      <x:c r="F24" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G24" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" s="18" t="str">
+        <x:v>desert_12</x:v>
+      </x:c>
+      <x:c r="B25" s="18" t="str">
+        <x:v>太陽祭司</x:v>
+      </x:c>
+      <x:c r="C25" s="18" t="str">
+        <x:v>desert</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E25" s="18" t="str">
+        <x:v>☀️</x:v>
+      </x:c>
+      <x:c r="F25" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G25" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
+      <x:c r="A26" s="18" t="str">
+        <x:v>swamp_1</x:v>
+      </x:c>
+      <x:c r="B26" s="18" t="str">
+        <x:v>劇毒蛙</x:v>
+      </x:c>
+      <x:c r="C26" s="18" t="str">
+        <x:v>swamp</x:v>
+      </x:c>
+      <x:c r="D26" s="18" t="str">
+        <x:v>poison</x:v>
+      </x:c>
+      <x:c r="E26" s="18" t="str">
+        <x:v>🐸</x:v>
+      </x:c>
+      <x:c r="F26" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G26" s="20" t="str">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="18" t="str">
+        <x:v>swamp_2</x:v>
+      </x:c>
+      <x:c r="B27" s="18" t="str">
+        <x:v>沼澤鱷</x:v>
+      </x:c>
+      <x:c r="C27" s="18" t="str">
+        <x:v>swamp</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E27" s="18" t="str">
+        <x:v>🐊</x:v>
+      </x:c>
+      <x:c r="F27" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G27" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="18" t="str">
+        <x:v>swamp_3</x:v>
+      </x:c>
+      <x:c r="B28" s="18" t="str">
+        <x:v>巨型水蛭</x:v>
+      </x:c>
+      <x:c r="C28" s="18" t="str">
+        <x:v>swamp</x:v>
+      </x:c>
+      <x:c r="D28" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E28" s="18" t="str">
+        <x:v>🪱</x:v>
+      </x:c>
+      <x:c r="F28" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G28" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="18" t="str">
+        <x:v>swamp_4</x:v>
+      </x:c>
+      <x:c r="B29" s="18" t="str">
+        <x:v>瘴氣幽魂</x:v>
+      </x:c>
+      <x:c r="C29" s="18" t="str">
+        <x:v>swamp</x:v>
+      </x:c>
+      <x:c r="D29" s="18" t="str">
+        <x:v>poison</x:v>
+      </x:c>
+      <x:c r="E29" s="18" t="str">
+        <x:v>👻</x:v>
+      </x:c>
+      <x:c r="F29" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G29" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="18" t="str">
+        <x:v>swamp_5</x:v>
+      </x:c>
+      <x:c r="B30" s="18" t="str">
+        <x:v>食人花</x:v>
+      </x:c>
+      <x:c r="C30" s="18" t="str">
+        <x:v>swamp</x:v>
+      </x:c>
+      <x:c r="D30" s="18" t="str">
+        <x:v>poison</x:v>
+      </x:c>
+      <x:c r="E30" s="18" t="str">
+        <x:v>🌺</x:v>
+      </x:c>
+      <x:c r="F30" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G30" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" s="18" t="str">
+        <x:v>swamp_6</x:v>
+      </x:c>
+      <x:c r="B31" s="18" t="str">
+        <x:v>泥漿怪</x:v>
+      </x:c>
+      <x:c r="C31" s="18" t="str">
+        <x:v>swamp</x:v>
+      </x:c>
+      <x:c r="D31" s="18" t="str">
+        <x:v>poison</x:v>
+      </x:c>
+      <x:c r="E31" s="18" t="str">
+        <x:v>🫠</x:v>
+      </x:c>
+      <x:c r="F31" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G31" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
+      <x:c r="A32" s="18" t="str">
+        <x:v>swamp_7</x:v>
+      </x:c>
+      <x:c r="B32" s="18" t="str">
+        <x:v>毒蚊群</x:v>
+      </x:c>
+      <x:c r="C32" s="18" t="str">
+        <x:v>swamp</x:v>
+      </x:c>
+      <x:c r="D32" s="18" t="str">
+        <x:v>poison</x:v>
+      </x:c>
+      <x:c r="E32" s="18" t="str">
+        <x:v>🦟</x:v>
+      </x:c>
+      <x:c r="F32" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G32" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
+      <x:c r="A33" s="18" t="str">
+        <x:v>swamp_8</x:v>
+      </x:c>
+      <x:c r="B33" s="18" t="str">
+        <x:v>沼澤巫婆</x:v>
+      </x:c>
+      <x:c r="C33" s="18" t="str">
+        <x:v>swamp</x:v>
+      </x:c>
+      <x:c r="D33" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E33" s="18" t="str">
+        <x:v>🧙</x:v>
+      </x:c>
+      <x:c r="F33" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G33" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
+      <x:c r="A34" s="18" t="str">
+        <x:v>swamp_9</x:v>
+      </x:c>
+      <x:c r="B34" s="18" t="str">
+        <x:v>腐爛樹人</x:v>
+      </x:c>
+      <x:c r="C34" s="18" t="str">
+        <x:v>swamp</x:v>
+      </x:c>
+      <x:c r="D34" s="18" t="str">
+        <x:v>poison</x:v>
+      </x:c>
+      <x:c r="E34" s="18" t="str">
+        <x:v>🌳</x:v>
+      </x:c>
+      <x:c r="F34" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G34" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
+      <x:c r="A35" s="18" t="str">
+        <x:v>swamp_10</x:v>
+      </x:c>
+      <x:c r="B35" s="18" t="str">
+        <x:v>蜥蜴薩滿</x:v>
+      </x:c>
+      <x:c r="C35" s="18" t="str">
+        <x:v>swamp</x:v>
+      </x:c>
+      <x:c r="D35" s="18" t="str">
+        <x:v>lightning</x:v>
+      </x:c>
+      <x:c r="E35" s="18" t="str">
+        <x:v>🦎</x:v>
+      </x:c>
+      <x:c r="F35" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G35" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
+      <x:c r="A36" s="18" t="str">
+        <x:v>swamp_11</x:v>
+      </x:c>
+      <x:c r="B36" s="18" t="str">
+        <x:v>深沼水蛇</x:v>
+      </x:c>
+      <x:c r="C36" s="18" t="str">
+        <x:v>swamp</x:v>
+      </x:c>
+      <x:c r="D36" s="18" t="str">
+        <x:v>ice</x:v>
+      </x:c>
+      <x:c r="E36" s="18" t="str">
+        <x:v>🐍</x:v>
+      </x:c>
+      <x:c r="F36" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G36" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="15" hidden="0" customHeight="1">
+      <x:c r="A37" s="18" t="str">
+        <x:v>swamp_12</x:v>
+      </x:c>
+      <x:c r="B37" s="18" t="str">
+        <x:v>沼澤霸主</x:v>
+      </x:c>
+      <x:c r="C37" s="18" t="str">
+        <x:v>swamp</x:v>
+      </x:c>
+      <x:c r="D37" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E37" s="18" t="str">
+        <x:v>🐲</x:v>
+      </x:c>
+      <x:c r="F37" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G37" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="15" hidden="0" customHeight="1">
+      <x:c r="A38" s="18" t="str">
+        <x:v>undead_skeleton</x:v>
+      </x:c>
+      <x:c r="B38" s="18" t="str">
+        <x:v>骸骨戰士</x:v>
+      </x:c>
+      <x:c r="C38" s="18" t="str">
+        <x:v>undead_mountains</x:v>
+      </x:c>
+      <x:c r="D38" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E38" s="18" t="str">
+        <x:v>skeleton</x:v>
+      </x:c>
+      <x:c r="F38" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G38" s="20" t="str">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="15" hidden="0" customHeight="1">
+      <x:c r="A39" s="18" t="str">
+        <x:v>undead_wraith</x:v>
+      </x:c>
+      <x:c r="B39" s="18" t="str">
+        <x:v>山脈怨靈</x:v>
+      </x:c>
+      <x:c r="C39" s="18" t="str">
+        <x:v>undead_mountains</x:v>
+      </x:c>
+      <x:c r="D39" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E39" s="18" t="str">
+        <x:v>wraith</x:v>
+      </x:c>
+      <x:c r="F39" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G39" s="20" t="str">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="15" hidden="0" customHeight="1">
+      <x:c r="A40" s="18" t="str">
+        <x:v>undead_ghoul</x:v>
+      </x:c>
+      <x:c r="B40" s="18" t="str">
+        <x:v>腐屍獵犬</x:v>
+      </x:c>
+      <x:c r="C40" s="18" t="str">
+        <x:v>undead_mountains</x:v>
+      </x:c>
+      <x:c r="D40" s="18" t="str">
+        <x:v>poison</x:v>
+      </x:c>
+      <x:c r="E40" s="18" t="str">
+        <x:v>ghoul</x:v>
+      </x:c>
+      <x:c r="F40" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G40" s="20" t="str">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="15" hidden="0" customHeight="1">
+      <x:c r="A41" s="18" t="str">
+        <x:v>undead_knight</x:v>
+      </x:c>
+      <x:c r="B41" s="18" t="str">
+        <x:v>亡靈騎士</x:v>
+      </x:c>
+      <x:c r="C41" s="18" t="str">
+        <x:v>undead_mountains</x:v>
+      </x:c>
+      <x:c r="D41" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E41" s="18" t="str">
+        <x:v>knight</x:v>
+      </x:c>
+      <x:c r="F41" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G41" s="20" t="str">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="15" hidden="0" customHeight="1">
+      <x:c r="A42" s="18" t="str">
+        <x:v>undead_banshee</x:v>
+      </x:c>
+      <x:c r="B42" s="18" t="str">
+        <x:v>哀嚎女妖</x:v>
+      </x:c>
+      <x:c r="C42" s="18" t="str">
+        <x:v>undead_mountains</x:v>
+      </x:c>
+      <x:c r="D42" s="18" t="str">
+        <x:v>ice</x:v>
+      </x:c>
+      <x:c r="E42" s="18" t="str">
+        <x:v>banshee</x:v>
+      </x:c>
+      <x:c r="F42" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G42" s="20" t="str">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="15" hidden="0" customHeight="1">
+      <x:c r="A43" s="18" t="str">
+        <x:v>undead_golem</x:v>
+      </x:c>
+      <x:c r="B43" s="18" t="str">
+        <x:v>墓石巨像</x:v>
+      </x:c>
+      <x:c r="C43" s="18" t="str">
+        <x:v>undead_mountains</x:v>
+      </x:c>
+      <x:c r="D43" s="18" t="str">
+        <x:v>earth</x:v>
+      </x:c>
+      <x:c r="E43" s="18" t="str">
+        <x:v>golem</x:v>
+      </x:c>
+      <x:c r="F43" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G43" s="20" t="str">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="15" hidden="0" customHeight="1">
+      <x:c r="A44" s="18" t="str">
+        <x:v>undead_vampire</x:v>
+      </x:c>
+      <x:c r="B44" s="18" t="str">
+        <x:v>血月伯爵</x:v>
+      </x:c>
+      <x:c r="C44" s="18" t="str">
+        <x:v>undead_mountains</x:v>
+      </x:c>
+      <x:c r="D44" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E44" s="18" t="str">
+        <x:v>vampire</x:v>
+      </x:c>
+      <x:c r="F44" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G44" s="20" t="str">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="15" hidden="0" customHeight="1">
+      <x:c r="A45" s="18" t="str">
         <x:v>undead_dragon</x:v>
       </x:c>
-      <x:c r="B9" s="18" t="str">
+      <x:c r="B45" s="18" t="str">
         <x:v>骨龍</x:v>
       </x:c>
-      <x:c r="C9" s="18" t="str">
+      <x:c r="C45" s="18" t="str">
+        <x:v>undead_mountains</x:v>
+      </x:c>
+      <x:c r="D45" s="18" t="str">
         <x:v>fire</x:v>
       </x:c>
-      <x:c r="D9" s="18" t="str">
+      <x:c r="E45" s="18" t="str">
         <x:v>dragon</x:v>
       </x:c>
-      <x:c r="E9" s="20" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="20" t="str">
+      <x:c r="F45" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G45" s="20" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G9" s="20" t="str">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="H9" s="20" t="str">
-        <x:v>1.4</x:v>
-      </x:c>
-      <x:c r="I9" s="20" t="str">
+    </x:row>
+    <x:row r="46" ht="15" hidden="0" customHeight="1">
+      <x:c r="A46" s="18" t="str">
+        <x:v>god_battlefield_1</x:v>
+      </x:c>
+      <x:c r="B46" s="18" t="str">
+        <x:v>太古戰魂</x:v>
+      </x:c>
+      <x:c r="C46" s="18" t="str">
+        <x:v>god_battlefield</x:v>
+      </x:c>
+      <x:c r="D46" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E46" s="18" t="str">
+        <x:v>👻</x:v>
+      </x:c>
+      <x:c r="F46" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G46" s="20" t="str">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="15" hidden="0" customHeight="1">
+      <x:c r="A47" s="18" t="str">
+        <x:v>god_battlefield_2</x:v>
+      </x:c>
+      <x:c r="B47" s="18" t="str">
+        <x:v>遠古神兵</x:v>
+      </x:c>
+      <x:c r="C47" s="18" t="str">
+        <x:v>god_battlefield</x:v>
+      </x:c>
+      <x:c r="D47" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E47" s="18" t="str">
+        <x:v>🗡️</x:v>
+      </x:c>
+      <x:c r="F47" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G47" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="15" hidden="0" customHeight="1">
+      <x:c r="A48" s="18" t="str">
+        <x:v>god_battlefield_3</x:v>
+      </x:c>
+      <x:c r="B48" s="18" t="str">
+        <x:v>破天戰將</x:v>
+      </x:c>
+      <x:c r="C48" s="18" t="str">
+        <x:v>god_battlefield</x:v>
+      </x:c>
+      <x:c r="D48" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E48" s="18" t="str">
+        <x:v>🛡️</x:v>
+      </x:c>
+      <x:c r="F48" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G48" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="15" hidden="0" customHeight="1">
+      <x:c r="A49" s="18" t="str">
+        <x:v>god_battlefield_4</x:v>
+      </x:c>
+      <x:c r="B49" s="18" t="str">
+        <x:v>烈焰神衛</x:v>
+      </x:c>
+      <x:c r="C49" s="18" t="str">
+        <x:v>god_battlefield</x:v>
+      </x:c>
+      <x:c r="D49" s="18" t="str">
+        <x:v>fire</x:v>
+      </x:c>
+      <x:c r="E49" s="18" t="str">
+        <x:v>💥</x:v>
+      </x:c>
+      <x:c r="F49" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G49" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="15" hidden="0" customHeight="1">
+      <x:c r="A50" s="18" t="str">
+        <x:v>god_battlefield_5</x:v>
+      </x:c>
+      <x:c r="B50" s="18" t="str">
+        <x:v>狂暴泰坦</x:v>
+      </x:c>
+      <x:c r="C50" s="18" t="str">
+        <x:v>god_battlefield</x:v>
+      </x:c>
+      <x:c r="D50" s="18" t="str">
+        <x:v>lightning</x:v>
+      </x:c>
+      <x:c r="E50" s="18" t="str">
+        <x:v>🗿</x:v>
+      </x:c>
+      <x:c r="F50" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G50" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="15" hidden="0" customHeight="1">
+      <x:c r="A51" s="18" t="str">
+        <x:v>god_battlefield_6</x:v>
+      </x:c>
+      <x:c r="B51" s="18" t="str">
+        <x:v>神魔殘骸</x:v>
+      </x:c>
+      <x:c r="C51" s="18" t="str">
+        <x:v>god_battlefield</x:v>
+      </x:c>
+      <x:c r="D51" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E51" s="18" t="str">
+        <x:v>☠️</x:v>
+      </x:c>
+      <x:c r="F51" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G51" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="15" hidden="0" customHeight="1">
+      <x:c r="A52" s="18" t="str">
+        <x:v>god_battlefield_7</x:v>
+      </x:c>
+      <x:c r="B52" s="18" t="str">
+        <x:v>不朽英靈</x:v>
+      </x:c>
+      <x:c r="C52" s="18" t="str">
+        <x:v>god_battlefield</x:v>
+      </x:c>
+      <x:c r="D52" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E52" s="18" t="str">
+        <x:v>🌟</x:v>
+      </x:c>
+      <x:c r="F52" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G52" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="15" hidden="0" customHeight="1">
+      <x:c r="A53" s="18" t="str">
+        <x:v>god_battlefield_8</x:v>
+      </x:c>
+      <x:c r="B53" s="18" t="str">
+        <x:v>裁決之劍</x:v>
+      </x:c>
+      <x:c r="C53" s="18" t="str">
+        <x:v>god_battlefield</x:v>
+      </x:c>
+      <x:c r="D53" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E53" s="18" t="str">
+        <x:v>⚔️</x:v>
+      </x:c>
+      <x:c r="F53" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G53" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="15" hidden="0" customHeight="1">
+      <x:c r="A54" s="18" t="str">
+        <x:v>god_battlefield_9</x:v>
+      </x:c>
+      <x:c r="B54" s="18" t="str">
+        <x:v>滅世魔將</x:v>
+      </x:c>
+      <x:c r="C54" s="18" t="str">
+        <x:v>god_battlefield</x:v>
+      </x:c>
+      <x:c r="D54" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E54" s="18" t="str">
+        <x:v>👹</x:v>
+      </x:c>
+      <x:c r="F54" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G54" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="15" hidden="0" customHeight="1">
+      <x:c r="A55" s="18" t="str">
+        <x:v>god_battlefield_10</x:v>
+      </x:c>
+      <x:c r="B55" s="18" t="str">
+        <x:v>太古龍魂</x:v>
+      </x:c>
+      <x:c r="C55" s="18" t="str">
+        <x:v>god_battlefield</x:v>
+      </x:c>
+      <x:c r="D55" s="18" t="str">
+        <x:v>lightning</x:v>
+      </x:c>
+      <x:c r="E55" s="18" t="str">
+        <x:v>🐉</x:v>
+      </x:c>
+      <x:c r="F55" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G55" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="15" hidden="0" customHeight="1">
+      <x:c r="A56" s="18" t="str">
+        <x:v>god_battlefield_11</x:v>
+      </x:c>
+      <x:c r="B56" s="18" t="str">
+        <x:v>戰爭主宰</x:v>
+      </x:c>
+      <x:c r="C56" s="18" t="str">
+        <x:v>god_battlefield</x:v>
+      </x:c>
+      <x:c r="D56" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E56" s="18" t="str">
+        <x:v>🔱</x:v>
+      </x:c>
+      <x:c r="F56" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G56" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="15" hidden="0" customHeight="1">
+      <x:c r="A57" s="18" t="str">
+        <x:v>god_battlefield_12</x:v>
+      </x:c>
+      <x:c r="B57" s="18" t="str">
+        <x:v>殞星巨獸</x:v>
+      </x:c>
+      <x:c r="C57" s="18" t="str">
+        <x:v>god_battlefield</x:v>
+      </x:c>
+      <x:c r="D57" s="18" t="str">
+        <x:v>fire</x:v>
+      </x:c>
+      <x:c r="E57" s="18" t="str">
+        <x:v>☄️</x:v>
+      </x:c>
+      <x:c r="F57" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G57" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="15" hidden="0" customHeight="1">
+      <x:c r="A58" s="18" t="str">
+        <x:v>god_chaos_1</x:v>
+      </x:c>
+      <x:c r="B58" s="18" t="str">
+        <x:v>混沌幼獸</x:v>
+      </x:c>
+      <x:c r="C58" s="18" t="str">
+        <x:v>god_chaos</x:v>
+      </x:c>
+      <x:c r="D58" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E58" s="18" t="str">
+        <x:v>🐾</x:v>
+      </x:c>
+      <x:c r="F58" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G58" s="20" t="str">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="15" hidden="0" customHeight="1">
+      <x:c r="A59" s="18" t="str">
+        <x:v>god_chaos_2</x:v>
+      </x:c>
+      <x:c r="B59" s="18" t="str">
+        <x:v>虛空行者</x:v>
+      </x:c>
+      <x:c r="C59" s="18" t="str">
+        <x:v>god_chaos</x:v>
+      </x:c>
+      <x:c r="D59" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E59" s="18" t="str">
+        <x:v>🌌</x:v>
+      </x:c>
+      <x:c r="F59" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G59" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="15" hidden="0" customHeight="1">
+      <x:c r="A60" s="18" t="str">
+        <x:v>god_chaos_3</x:v>
+      </x:c>
+      <x:c r="B60" s="18" t="str">
+        <x:v>時空魔靈</x:v>
+      </x:c>
+      <x:c r="C60" s="18" t="str">
+        <x:v>god_chaos</x:v>
+      </x:c>
+      <x:c r="D60" s="18" t="str">
+        <x:v>lightning</x:v>
+      </x:c>
+      <x:c r="E60" s="18" t="str">
+        <x:v>⏱️</x:v>
+      </x:c>
+      <x:c r="F60" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G60" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="15" hidden="0" customHeight="1">
+      <x:c r="A61" s="18" t="str">
+        <x:v>god_chaos_4</x:v>
+      </x:c>
+      <x:c r="B61" s="18" t="str">
+        <x:v>裂縫幻影</x:v>
+      </x:c>
+      <x:c r="C61" s="18" t="str">
+        <x:v>god_chaos</x:v>
+      </x:c>
+      <x:c r="D61" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E61" s="18" t="str">
+        <x:v>👥</x:v>
+      </x:c>
+      <x:c r="F61" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G61" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="15" hidden="0" customHeight="1">
+      <x:c r="A62" s="18" t="str">
+        <x:v>god_chaos_5</x:v>
+      </x:c>
+      <x:c r="B62" s="18" t="str">
+        <x:v>混沌噬魂獸</x:v>
+      </x:c>
+      <x:c r="C62" s="18" t="str">
+        <x:v>god_chaos</x:v>
+      </x:c>
+      <x:c r="D62" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E62" s="18" t="str">
+        <x:v>👾</x:v>
+      </x:c>
+      <x:c r="F62" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G62" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="15" hidden="0" customHeight="1">
+      <x:c r="A63" s="18" t="str">
+        <x:v>god_chaos_6</x:v>
+      </x:c>
+      <x:c r="B63" s="18" t="str">
+        <x:v>蝕天巨煞</x:v>
+      </x:c>
+      <x:c r="C63" s="18" t="str">
+        <x:v>god_chaos</x:v>
+      </x:c>
+      <x:c r="D63" s="18" t="str">
+        <x:v>poison</x:v>
+      </x:c>
+      <x:c r="E63" s="18" t="str">
+        <x:v>👹</x:v>
+      </x:c>
+      <x:c r="F63" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G63" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="15" hidden="0" customHeight="1">
+      <x:c r="A64" s="18" t="str">
+        <x:v>god_chaos_7</x:v>
+      </x:c>
+      <x:c r="B64" s="18" t="str">
+        <x:v>虛空之眼</x:v>
+      </x:c>
+      <x:c r="C64" s="18" t="str">
+        <x:v>god_chaos</x:v>
+      </x:c>
+      <x:c r="D64" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E64" s="18" t="str">
+        <x:v>👁️</x:v>
+      </x:c>
+      <x:c r="F64" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G64" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="15" hidden="0" customHeight="1">
+      <x:c r="A65" s="18" t="str">
+        <x:v>god_chaos_8</x:v>
+      </x:c>
+      <x:c r="B65" s="18" t="str">
+        <x:v>元素狂暴體</x:v>
+      </x:c>
+      <x:c r="C65" s="18" t="str">
+        <x:v>god_chaos</x:v>
+      </x:c>
+      <x:c r="D65" s="18" t="str">
+        <x:v>lightning</x:v>
+      </x:c>
+      <x:c r="E65" s="18" t="str">
+        <x:v>⚡</x:v>
+      </x:c>
+      <x:c r="F65" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G65" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="15" hidden="0" customHeight="1">
+      <x:c r="A66" s="18" t="str">
+        <x:v>god_chaos_9</x:v>
+      </x:c>
+      <x:c r="B66" s="18" t="str">
+        <x:v>混沌使者</x:v>
+      </x:c>
+      <x:c r="C66" s="18" t="str">
+        <x:v>god_chaos</x:v>
+      </x:c>
+      <x:c r="D66" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E66" s="18" t="str">
+        <x:v>🔮</x:v>
+      </x:c>
+      <x:c r="F66" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G66" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="15" hidden="0" customHeight="1">
+      <x:c r="A67" s="18" t="str">
+        <x:v>god_chaos_10</x:v>
+      </x:c>
+      <x:c r="B67" s="18" t="str">
+        <x:v>星雲魔獸</x:v>
+      </x:c>
+      <x:c r="C67" s="18" t="str">
+        <x:v>god_chaos</x:v>
+      </x:c>
+      <x:c r="D67" s="18" t="str">
+        <x:v>ice</x:v>
+      </x:c>
+      <x:c r="E67" s="18" t="str">
+        <x:v>🌌</x:v>
+      </x:c>
+      <x:c r="F67" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G67" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="15" hidden="0" customHeight="1">
+      <x:c r="A68" s="18" t="str">
+        <x:v>god_chaos_11</x:v>
+      </x:c>
+      <x:c r="B68" s="18" t="str">
+        <x:v>創世餘燼</x:v>
+      </x:c>
+      <x:c r="C68" s="18" t="str">
+        <x:v>god_chaos</x:v>
+      </x:c>
+      <x:c r="D68" s="18" t="str">
+        <x:v>fire</x:v>
+      </x:c>
+      <x:c r="E68" s="18" t="str">
+        <x:v>🔥</x:v>
+      </x:c>
+      <x:c r="F68" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G68" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="15" hidden="0" customHeight="1">
+      <x:c r="A69" s="18" t="str">
+        <x:v>god_chaos_12</x:v>
+      </x:c>
+      <x:c r="B69" s="18" t="str">
+        <x:v>混沌大天尊</x:v>
+      </x:c>
+      <x:c r="C69" s="18" t="str">
+        <x:v>god_chaos</x:v>
+      </x:c>
+      <x:c r="D69" s="18" t="str">
+        <x:v>dark</x:v>
+      </x:c>
+      <x:c r="E69" s="18" t="str">
+        <x:v>☸️</x:v>
+      </x:c>
+      <x:c r="F69" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G69" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="15" hidden="0" customHeight="1">
+      <x:c r="A70" s="18" t="str">
+        <x:v>god_sanctuary_1</x:v>
+      </x:c>
+      <x:c r="B70" s="18" t="str">
+        <x:v>巡天聖光</x:v>
+      </x:c>
+      <x:c r="C70" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="D70" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E70" s="18" t="str">
+        <x:v>💫</x:v>
+      </x:c>
+      <x:c r="F70" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G70" s="20" t="str">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="15" hidden="0" customHeight="1">
+      <x:c r="A71" s="18" t="str">
+        <x:v>god_sanctuary_2</x:v>
+      </x:c>
+      <x:c r="B71" s="18" t="str">
+        <x:v>熾天使</x:v>
+      </x:c>
+      <x:c r="C71" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="D71" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E71" s="18" t="str">
+        <x:v>👼</x:v>
+      </x:c>
+      <x:c r="F71" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G71" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="15" hidden="0" customHeight="1">
+      <x:c r="A72" s="18" t="str">
+        <x:v>god_sanctuary_3</x:v>
+      </x:c>
+      <x:c r="B72" s="18" t="str">
+        <x:v>智天使</x:v>
+      </x:c>
+      <x:c r="C72" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="D72" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E72" s="18" t="str">
+        <x:v>👼‍♀️</x:v>
+      </x:c>
+      <x:c r="F72" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G72" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="15" hidden="0" customHeight="1">
+      <x:c r="A73" s="18" t="str">
+        <x:v>god_sanctuary_4</x:v>
+      </x:c>
+      <x:c r="B73" s="18" t="str">
+        <x:v>審判使者</x:v>
+      </x:c>
+      <x:c r="C73" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="D73" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E73" s="18" t="str">
+        <x:v>⚖️</x:v>
+      </x:c>
+      <x:c r="F73" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G73" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="15" hidden="0" customHeight="1">
+      <x:c r="A74" s="18" t="str">
+        <x:v>god_sanctuary_5</x:v>
+      </x:c>
+      <x:c r="B74" s="18" t="str">
+        <x:v>聖域守衛</x:v>
+      </x:c>
+      <x:c r="C74" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="D74" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E74" s="18" t="str">
+        <x:v>🛡️</x:v>
+      </x:c>
+      <x:c r="F74" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G74" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="15" hidden="0" customHeight="1">
+      <x:c r="A75" s="18" t="str">
+        <x:v>god_sanctuary_6</x:v>
+      </x:c>
+      <x:c r="B75" s="18" t="str">
+        <x:v>曜光巨龍</x:v>
+      </x:c>
+      <x:c r="C75" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="D75" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E75" s="18" t="str">
+        <x:v>🐉</x:v>
+      </x:c>
+      <x:c r="F75" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G75" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="15" hidden="0" customHeight="1">
+      <x:c r="A76" s="18" t="str">
+        <x:v>god_sanctuary_7</x:v>
+      </x:c>
+      <x:c r="B76" s="18" t="str">
+        <x:v>神威巨像</x:v>
+      </x:c>
+      <x:c r="C76" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="D76" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E76" s="18" t="str">
+        <x:v>🏛️</x:v>
+      </x:c>
+      <x:c r="F76" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G76" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="15" hidden="0" customHeight="1">
+      <x:c r="A77" s="18" t="str">
+        <x:v>god_sanctuary_8</x:v>
+      </x:c>
+      <x:c r="B77" s="18" t="str">
+        <x:v>永恒靈體</x:v>
+      </x:c>
+      <x:c r="C77" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="D77" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E77" s="18" t="str">
+        <x:v>🕊️</x:v>
+      </x:c>
+      <x:c r="F77" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G77" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="15" hidden="0" customHeight="1">
+      <x:c r="A78" s="18" t="str">
+        <x:v>god_sanctuary_9</x:v>
+      </x:c>
+      <x:c r="B78" s="18" t="str">
+        <x:v>創世執法官</x:v>
+      </x:c>
+      <x:c r="C78" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="D78" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E78" s="18" t="str">
+        <x:v>📜</x:v>
+      </x:c>
+      <x:c r="F78" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G78" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="15" hidden="0" customHeight="1">
+      <x:c r="A79" s="18" t="str">
+        <x:v>god_sanctuary_10</x:v>
+      </x:c>
+      <x:c r="B79" s="18" t="str">
+        <x:v>神王護衛長</x:v>
+      </x:c>
+      <x:c r="C79" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="D79" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E79" s="18" t="str">
+        <x:v>👑</x:v>
+      </x:c>
+      <x:c r="F79" s="20" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G79" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="15" hidden="0" customHeight="1">
+      <x:c r="A80" s="18" t="str">
+        <x:v>god_sanctuary_11</x:v>
+      </x:c>
+      <x:c r="B80" s="18" t="str">
+        <x:v>諸神榮光</x:v>
+      </x:c>
+      <x:c r="C80" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="D80" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E80" s="18" t="str">
+        <x:v>🌟</x:v>
+      </x:c>
+      <x:c r="F80" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G80" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="15" hidden="0" customHeight="1">
+      <x:c r="A81" s="18" t="str">
+        <x:v>god_sanctuary_12</x:v>
+      </x:c>
+      <x:c r="B81" s="18" t="str">
+        <x:v>永恒神王</x:v>
+      </x:c>
+      <x:c r="C81" s="18" t="str">
+        <x:v>god_sanctuary</x:v>
+      </x:c>
+      <x:c r="D81" s="18" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E81" s="18" t="str">
+        <x:v>🌌</x:v>
+      </x:c>
+      <x:c r="F81" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G81" s="20" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6d582769836414f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra60086d77fe64783"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/config/Excel/NPC.xlsx
+++ b/config/Excel/NPC.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC" sheetId="1" r:id="R68ea60a2b86e4c8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC" sheetId="1" r:id="R59a95684e2c54893"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2237,7 +2237,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra60086d77fe64783"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a3aa16fea8c468e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/config/Excel/NPC.xlsx
+++ b/config/Excel/NPC.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC" sheetId="1" r:id="R59a95684e2c54893"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC" sheetId="1" r:id="Raf939a4231f34848"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2237,7 +2237,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a3aa16fea8c468e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15b76b4dfb9d4a01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/config/Excel/NPC.xlsx
+++ b/config/Excel/NPC.xlsx
@@ -1634,7 +1634,7 @@
         <v>55</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>45</v>
@@ -2096,7 +2096,7 @@
         <v>91</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>10</v>
+        <v>145</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>106</v>
@@ -2625,7 +2625,7 @@
         <v>158</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>51</v>
+        <v>145</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>45</v>
@@ -3223,7 +3223,7 @@
         <v>225</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>243</v>

--- a/config/Excel/NPC.xlsx
+++ b/config/Excel/NPC.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB1A9D5-EA7B-43F2-8A04-AA6A78DF7DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B524D9AA-7D79-4445-B38B-36307351D516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="299">
   <si>
     <t>NPC識別碼</t>
   </si>
@@ -57,15 +57,9 @@
     <t>出現權重</t>
   </si>
   <si>
-    <t>plains_1</t>
-  </si>
-  <si>
     <t>史萊姆</t>
   </si>
   <si>
-    <t>plains</t>
-  </si>
-  <si>
     <t>poison</t>
   </si>
   <si>
@@ -78,9 +72,6 @@
     <t>30</t>
   </si>
   <si>
-    <t>plains_2</t>
-  </si>
-  <si>
     <t>哥布林</t>
   </si>
   <si>
@@ -93,9 +84,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>plains_3</t>
-  </si>
-  <si>
     <t>野狼</t>
   </si>
   <si>
@@ -105,45 +93,30 @@
     <t>🐺</t>
   </si>
   <si>
-    <t>plains_4</t>
-  </si>
-  <si>
     <t>骷髏兵</t>
   </si>
   <si>
     <t>💀</t>
   </si>
   <si>
-    <t>plains_5</t>
-  </si>
-  <si>
     <t>暗影蝠</t>
   </si>
   <si>
     <t>🦇</t>
   </si>
   <si>
-    <t>plains_6</t>
-  </si>
-  <si>
     <t>樹妖</t>
   </si>
   <si>
     <t>🌳</t>
   </si>
   <si>
-    <t>plains_7</t>
-  </si>
-  <si>
     <t>蜥蜴戰士</t>
   </si>
   <si>
     <t>🦎</t>
   </si>
   <si>
-    <t>plains_8</t>
-  </si>
-  <si>
     <t>半獸人</t>
   </si>
   <si>
@@ -153,18 +126,12 @@
     <t>🐗</t>
   </si>
   <si>
-    <t>plains_9</t>
-  </si>
-  <si>
     <t>幽靈</t>
   </si>
   <si>
     <t>👻</t>
   </si>
   <si>
-    <t>plains_10</t>
-  </si>
-  <si>
     <t>石像鬼</t>
   </si>
   <si>
@@ -174,18 +141,12 @@
     <t>🗿</t>
   </si>
   <si>
-    <t>plains_11</t>
-  </si>
-  <si>
     <t>牛頭人</t>
   </si>
   <si>
     <t>🐂</t>
   </si>
   <si>
-    <t>plains_12</t>
-  </si>
-  <si>
     <t>雙足飛龍</t>
   </si>
   <si>
@@ -198,111 +159,57 @@
     <t>desert_1</t>
   </si>
   <si>
-    <t>沙漠蠍</t>
-  </si>
-  <si>
     <t>desert</t>
   </si>
   <si>
-    <t>🦂</t>
-  </si>
-  <si>
     <t>25</t>
   </si>
   <si>
     <t>desert_2</t>
   </si>
   <si>
-    <t>沙蟲</t>
-  </si>
-  <si>
     <t>🪱</t>
   </si>
   <si>
     <t>desert_3</t>
   </si>
   <si>
-    <t>木乃伊</t>
-  </si>
-  <si>
-    <t>🧟</t>
-  </si>
-  <si>
     <t>desert_4</t>
   </si>
   <si>
-    <t>沙漠禿鷹</t>
-  </si>
-  <si>
-    <t>🦅</t>
-  </si>
-  <si>
     <t>desert_5</t>
   </si>
   <si>
-    <t>響尾蛇</t>
-  </si>
-  <si>
     <t>🐍</t>
   </si>
   <si>
     <t>desert_6</t>
   </si>
   <si>
-    <t>沙魔</t>
-  </si>
-  <si>
     <t>👹</t>
   </si>
   <si>
     <t>desert_7</t>
   </si>
   <si>
-    <t>石化蜥蜴</t>
-  </si>
-  <si>
     <t>desert_8</t>
   </si>
   <si>
-    <t>沙漠強盜</t>
-  </si>
-  <si>
-    <t>🏴‍☠️</t>
-  </si>
-  <si>
     <t>desert_9</t>
   </si>
   <si>
-    <t>火焰精靈</t>
-  </si>
-  <si>
     <t>🔥</t>
   </si>
   <si>
     <t>desert_10</t>
   </si>
   <si>
-    <t>遠古石像</t>
-  </si>
-  <si>
     <t>desert_11</t>
   </si>
   <si>
-    <t>沙丘巨獸</t>
-  </si>
-  <si>
-    <t>🐫</t>
-  </si>
-  <si>
     <t>desert_12</t>
   </si>
   <si>
-    <t>太陽祭司</t>
-  </si>
-  <si>
-    <t>☀️</t>
-  </si>
-  <si>
     <t>swamp_1</t>
   </si>
   <si>
@@ -402,9 +309,6 @@
     <t>🐲</t>
   </si>
   <si>
-    <t>undead_skeleton</t>
-  </si>
-  <si>
     <t>骸骨戰士</t>
   </si>
   <si>
@@ -417,9 +321,6 @@
     <t>35</t>
   </si>
   <si>
-    <t>undead_wraith</t>
-  </si>
-  <si>
     <t>山脈怨靈</t>
   </si>
   <si>
@@ -429,9 +330,6 @@
     <t>18</t>
   </si>
   <si>
-    <t>undead_ghoul</t>
-  </si>
-  <si>
     <t>腐屍獵犬</t>
   </si>
   <si>
@@ -441,9 +339,6 @@
     <t>16</t>
   </si>
   <si>
-    <t>undead_knight</t>
-  </si>
-  <si>
     <t>亡靈騎士</t>
   </si>
   <si>
@@ -453,9 +348,6 @@
     <t>12</t>
   </si>
   <si>
-    <t>undead_banshee</t>
-  </si>
-  <si>
     <t>哀嚎女妖</t>
   </si>
   <si>
@@ -465,9 +357,6 @@
     <t>8</t>
   </si>
   <si>
-    <t>undead_golem</t>
-  </si>
-  <si>
     <t>墓石巨像</t>
   </si>
   <si>
@@ -480,9 +369,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>undead_vampire</t>
-  </si>
-  <si>
     <t>血月伯爵</t>
   </si>
   <si>
@@ -492,12 +378,6 @@
     <t>4</t>
   </si>
   <si>
-    <t>undead_dragon</t>
-  </si>
-  <si>
-    <t>骨龍</t>
-  </si>
-  <si>
     <t>dragon</t>
   </si>
   <si>
@@ -723,18 +603,12 @@
     <t>god_sanctuary_2</t>
   </si>
   <si>
-    <t>熾天使</t>
-  </si>
-  <si>
     <t>👼</t>
   </si>
   <si>
     <t>god_sanctuary_3</t>
   </si>
   <si>
-    <t>智天使</t>
-  </si>
-  <si>
     <t>👼‍♀️</t>
   </si>
   <si>
@@ -762,9 +636,6 @@
     <t>god_sanctuary_7</t>
   </si>
   <si>
-    <t>神威巨像</t>
-  </si>
-  <si>
     <t>🏛️</t>
   </si>
   <si>
@@ -780,9 +651,6 @@
     <t>god_sanctuary_9</t>
   </si>
   <si>
-    <t>創世執法官</t>
-  </si>
-  <si>
     <t>📜</t>
   </si>
   <si>
@@ -798,13 +666,7 @@
     <t>god_sanctuary_11</t>
   </si>
   <si>
-    <t>諸神榮光</t>
-  </si>
-  <si>
     <t>god_sanctuary_12</t>
-  </si>
-  <si>
-    <t>永恒神王</t>
   </si>
   <si>
     <t>毒</t>
@@ -988,40 +850,110 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">🐻‍❄️</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🧊</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🦍</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🧝‍♀️</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🌫️</t>
-  </si>
-  <si>
-    <t xml:space="preserve">❄️</t>
-  </si>
-  <si>
-    <t xml:space="preserve">💠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🏹</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rotting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">devourer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skeleton_mage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lost_soul</t>
+    <t>🐻‍❄️</t>
+  </si>
+  <si>
+    <t>🧊</t>
+  </si>
+  <si>
+    <t>🦍</t>
+  </si>
+  <si>
+    <t>🧝‍♀️</t>
+  </si>
+  <si>
+    <t>🌫️</t>
+  </si>
+  <si>
+    <t>❄️</t>
+  </si>
+  <si>
+    <t>💠</t>
+  </si>
+  <si>
+    <t>🏹</t>
+  </si>
+  <si>
+    <t>rotting</t>
+  </si>
+  <si>
+    <t>devourer</t>
+  </si>
+  <si>
+    <t>skeleton_mage</t>
+  </si>
+  <si>
+    <t>lost_soul</t>
+  </si>
+  <si>
+    <t>地</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icefield_1</t>
+  </si>
+  <si>
+    <t>冰原史萊姆</t>
+  </si>
+  <si>
+    <t>雷電魔像</t>
+  </si>
+  <si>
+    <t>冰墓幽靈</t>
+  </si>
+  <si>
+    <t>幽魂</t>
+  </si>
+  <si>
+    <t>寒冰魔像</t>
+  </si>
+  <si>
+    <t>骷髏弓箭手</t>
+  </si>
+  <si>
+    <t>undead_1</t>
+  </si>
+  <si>
+    <t>天使</t>
+  </si>
+  <si>
+    <t>天使巡狩</t>
+  </si>
+  <si>
+    <t>巨魔像</t>
+  </si>
+  <si>
+    <t>聖地執法者</t>
+  </si>
+  <si>
+    <t>智慧晶體</t>
+  </si>
+  <si>
+    <t>神聖執法官</t>
+  </si>
+  <si>
+    <t>fire</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>火蝙蝠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑暗女妖</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>閃電狼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dark</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ice</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1118,7 +1050,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1137,6 +1069,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1165,21 +1103,6 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="外觀"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="魔法型（1是／0否）"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="出現權重"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2B026043-47EE-4AAE-8C7D-05379B191467}" name="NPCTable3" displayName="NPCTable3" ref="A1:G81" totalsRowShown="0">
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{E066C8D2-1B16-4D90-A4BC-AC21ED8CD426}" name="NPC識別碼"/>
-    <tableColumn id="2" xr3:uid="{06D7BEE6-F962-412E-94D5-2E7365A38350}" name="NPC名稱"/>
-    <tableColumn id="3" xr3:uid="{9E7B3580-B663-4600-9D9B-3B8322627181}" name="所屬地圖識別碼"/>
-    <tableColumn id="4" xr3:uid="{13BFC4A0-B62A-47CC-9A60-1B8255F65ED5}" name="屬性"/>
-    <tableColumn id="5" xr3:uid="{8EE76AFB-9A1C-45BE-9657-E4A71BC51BBA}" name="外觀"/>
-    <tableColumn id="6" xr3:uid="{1BA33280-EFAF-4B71-A7F8-CF16A673BA9A}" name="魔法型（1是／0否）"/>
-    <tableColumn id="7" xr3:uid="{CAF036C2-C985-4472-9C53-34C9F9F15918}" name="出現權重"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1418,1936 +1341,1936 @@
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>292</v>
+        <v>246</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>293</v>
+        <v>247</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>271</v>
+        <v>225</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>312</v>
+        <v>266</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>313</v>
+        <v>267</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>295</v>
+        <v>249</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>296</v>
+        <v>250</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>272</v>
+        <v>226</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>314</v>
+        <v>268</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>297</v>
+        <v>251</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>298</v>
+        <v>252</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>315</v>
+        <v>269</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>316</v>
+        <v>270</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>300</v>
+        <v>254</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>317</v>
+        <v>271</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K22" s="7"/>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>274</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>318</v>
+        <v>272</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>319</v>
+        <v>273</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>303</v>
+        <v>257</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>273</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K28" s="7"/>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>279</v>
+        <v>233</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>281</v>
+        <v>235</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>283</v>
+        <v>237</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>284</v>
+        <v>238</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>146</v>
+        <v>109</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>147</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>285</v>
+        <v>239</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>275</v>
+        <v>229</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>320</v>
+        <v>274</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>287</v>
+        <v>241</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>276</v>
+        <v>230</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>321</v>
+        <v>275</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>288</v>
+        <v>242</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>277</v>
+        <v>231</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>322</v>
+        <v>276</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>147</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>289</v>
+        <v>243</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>323</v>
+        <v>277</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>290</v>
+        <v>244</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>291</v>
+        <v>245</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>157</v>
+        <v>117</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>161</v>
+        <v>121</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>166</v>
+        <v>126</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>167</v>
+        <v>127</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>184</v>
+        <v>144</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>193</v>
+        <v>153</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>194</v>
+        <v>154</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>199</v>
+        <v>159</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>201</v>
+        <v>161</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>206</v>
+        <v>166</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>209</v>
+        <v>169</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>214</v>
+        <v>174</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>217</v>
+        <v>177</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>218</v>
+        <v>178</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>222</v>
+        <v>182</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>226</v>
+        <v>186</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>263</v>
+        <v>217</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>231</v>
+        <v>190</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>264</v>
+        <v>218</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>234</v>
+        <v>192</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>240</v>
+        <v>198</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>241</v>
+        <v>199</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>269</v>
+        <v>223</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>244</v>
+        <v>201</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>245</v>
+        <v>202</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>246</v>
+        <v>203</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>268</v>
+        <v>222</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>249</v>
+        <v>205</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>266</v>
+        <v>220</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>252</v>
+        <v>208</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>253</v>
+        <v>209</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>267</v>
+        <v>221</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>265</v>
+        <v>219</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3361,7 +3284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB49652-7DC2-4CB9-8BC9-BBF4428EE3D9}">
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -3369,8 +3292,9 @@
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="6" max="6" width="18" style="9" customWidth="1"/>
+    <col min="7" max="7" width="14" style="9" customWidth="1"/>
+    <col min="8" max="8" width="3.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15">
@@ -3398,1885 +3322,2316 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="C2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>13</v>
+      <c r="F2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="8">
+        <v>10</v>
+      </c>
+      <c r="I2" t="str">
+        <f>VLOOKUP(D2,$N$4:$O$10,2,0)</f>
+        <v>地</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>18</v>
+      <c r="F3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="8">
+        <v>1</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I66" si="0">VLOOKUP(D3,$N$4:$O$10,2,0)</f>
+        <v>火</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>108</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8">
+        <v>1</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="0"/>
+        <v>地</v>
+      </c>
       <c r="N4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>257</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75">
       <c r="A5" s="2" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
+        <v>108</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="8">
+        <v>1</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="0"/>
+        <v>地</v>
       </c>
       <c r="N5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>258</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.75">
       <c r="A6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>294</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
+        <v>293</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="0"/>
+        <v>火</v>
+      </c>
+      <c r="N6" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N6" t="s">
-        <v>37</v>
-      </c>
       <c r="O6" s="5" t="s">
-        <v>259</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.75">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>108</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="8">
+        <v>1</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="0"/>
+        <v>地</v>
       </c>
       <c r="N7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.75">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="8">
+        <v>10</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="0"/>
+        <v>火</v>
+      </c>
+      <c r="N8" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" t="s">
-        <v>44</v>
-      </c>
       <c r="O8" s="5" t="s">
-        <v>261</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.75">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>108</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="8">
+        <v>1</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="0"/>
+        <v>地</v>
+      </c>
+      <c r="N9" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" t="s">
-        <v>51</v>
-      </c>
       <c r="O9" s="5" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="15.75">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>18</v>
+        <v>31</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="8">
+        <v>1</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="0"/>
+        <v>暗</v>
+      </c>
+      <c r="N10" t="s">
+        <v>108</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>108</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="8">
+        <v>1</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="0"/>
+        <v>地</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>37</v>
+        <v>293</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>18</v>
+        <v>36</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="8">
+        <v>1</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="0"/>
+        <v>火</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>293</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="8">
+        <v>1</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="0"/>
+        <v>火</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15">
+      <c r="A14" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>57</v>
+      <c r="F14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="8">
+        <v>10</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="0"/>
+        <v>電</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="2" t="s">
-        <v>58</v>
+        <v>247</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>59</v>
+        <v>225</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>55</v>
+        <v>258</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>18</v>
+        <v>266</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="0"/>
+        <v>冰</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="0"/>
+        <v>冰</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="0"/>
+        <v>電</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="8">
+        <v>10</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="0"/>
+        <v>冰</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="0"/>
+        <v>冰</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15">
+      <c r="A20" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="0"/>
+        <v>暗</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" t="str">
+        <f t="shared" si="0"/>
+        <v>電</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" t="str">
+        <f t="shared" si="0"/>
+        <v>冰</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" t="str">
+        <f t="shared" si="0"/>
+        <v>冰</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="0"/>
+        <v>電</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="0"/>
+        <v>冰</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F26" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="8">
+        <v>10</v>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="0"/>
+        <v>毒</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F27" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="8">
+        <v>10</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="0"/>
+        <v>暗</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="2" t="s">
+      <c r="B28" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="0"/>
+        <v>暗</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="2" t="s">
+      <c r="C29" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="0"/>
+        <v>毒</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="C30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="2" t="s">
+      <c r="F30" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="0"/>
+        <v>毒</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="C31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" si="0"/>
+        <v>地</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" t="str">
+        <f t="shared" si="0"/>
+        <v>毒</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" si="0"/>
+        <v>暗</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" t="str">
+        <f t="shared" si="0"/>
+        <v>毒</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" t="str">
+        <f t="shared" si="0"/>
+        <v>暗</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" t="str">
+        <f t="shared" si="0"/>
+        <v>毒</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" t="str">
+        <f t="shared" si="0"/>
+        <v>暗</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="8">
+        <v>10</v>
+      </c>
+      <c r="I38" t="str">
+        <f t="shared" si="0"/>
+        <v>暗</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" t="str">
+        <f t="shared" si="0"/>
+        <v>暗</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="8">
+        <v>10</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" si="0"/>
+        <v>毒</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="0"/>
+        <v>暗</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" t="str">
+        <f t="shared" si="0"/>
+        <v>暗</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" t="str">
+        <f t="shared" si="0"/>
+        <v>地</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" t="str">
+        <f t="shared" si="0"/>
+        <v>火</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" t="str">
+        <f t="shared" si="0"/>
+        <v>毒</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" t="str">
+        <f t="shared" si="0"/>
+        <v>暗</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" t="str">
+        <f t="shared" si="0"/>
+        <v>毒</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" t="str">
+        <f t="shared" si="0"/>
+        <v>暗</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I49" t="str">
+        <f t="shared" si="0"/>
+        <v>暗</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="8">
+        <v>10</v>
+      </c>
+      <c r="I50" t="str">
+        <f t="shared" si="0"/>
+        <v>地</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I51" t="str">
+        <f t="shared" si="0"/>
+        <v>地</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I52" t="str">
+        <f t="shared" si="0"/>
+        <v>地</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" t="str">
+        <f t="shared" si="0"/>
+        <v>火</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B32" s="2" t="s">
+      <c r="F54" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" t="str">
+        <f t="shared" si="0"/>
+        <v>地</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I55" t="str">
+        <f t="shared" si="0"/>
+        <v>火</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B36" s="2" t="s">
+      <c r="E56" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" t="str">
+        <f t="shared" si="0"/>
+        <v>地</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="D57" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" s="8">
+        <v>10</v>
+      </c>
+      <c r="I57" t="str">
+        <f t="shared" si="0"/>
+        <v>火</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I58" t="str">
+        <f t="shared" si="0"/>
+        <v>暗</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" t="str">
+        <f t="shared" si="0"/>
+        <v>火</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I60" t="str">
+        <f t="shared" si="0"/>
+        <v>火</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" t="str">
+        <f t="shared" si="0"/>
+        <v>火</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="8">
+        <v>10</v>
+      </c>
+      <c r="I62" t="str">
+        <f t="shared" si="0"/>
+        <v>電</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I63" t="str">
+        <f t="shared" si="0"/>
+        <v>冰</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" t="str">
+        <f t="shared" si="0"/>
+        <v>冰</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" t="str">
+        <f t="shared" si="0"/>
+        <v>冰</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" t="str">
+        <f t="shared" si="0"/>
+        <v>電</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I67" t="str">
+        <f t="shared" ref="I67:I85" si="1">VLOOKUP(D67,$N$4:$O$10,2,0)</f>
+        <v>冰</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D68" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I68" t="str">
+        <f t="shared" si="1"/>
+        <v>暗</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G69" s="8">
+        <v>10</v>
+      </c>
+      <c r="I69" t="str">
+        <f t="shared" si="1"/>
+        <v>電</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" t="str">
+        <f t="shared" si="1"/>
+        <v>電</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" t="str">
+        <f t="shared" si="1"/>
+        <v>冰</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I72" t="str">
+        <f t="shared" si="1"/>
+        <v>電</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I73" t="str">
+        <f t="shared" si="1"/>
+        <v>冰</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G74" s="8">
+        <v>10</v>
+      </c>
+      <c r="I74" t="str">
+        <f t="shared" si="1"/>
+        <v>聖</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G75" s="8">
+        <v>5</v>
+      </c>
+      <c r="I75" t="str">
+        <f t="shared" si="1"/>
+        <v>聖</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G76" s="8">
+        <v>5</v>
+      </c>
+      <c r="I76" t="str">
+        <f t="shared" si="1"/>
+        <v>聖</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I77" t="str">
+        <f t="shared" si="1"/>
+        <v>火</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="2" t="s">
+      <c r="F78" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G78" s="8">
+        <v>5</v>
+      </c>
+      <c r="I78" t="str">
+        <f t="shared" si="1"/>
+        <v>聖</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" t="str">
+        <f t="shared" si="1"/>
+        <v>聖</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I80" t="str">
+        <f t="shared" si="1"/>
+        <v>地</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I81" t="str">
+        <f t="shared" si="1"/>
+        <v>電</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" t="s">
+        <v>204</v>
+      </c>
+      <c r="B82" t="s">
+        <v>290</v>
+      </c>
+      <c r="C82" t="s">
+        <v>185</v>
+      </c>
+      <c r="D82" t="s">
+        <v>33</v>
+      </c>
+      <c r="E82" t="s">
+        <v>205</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I82" t="str">
+        <f t="shared" si="1"/>
+        <v>聖</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" t="s">
+        <v>206</v>
+      </c>
+      <c r="B83" t="s">
+        <v>207</v>
+      </c>
+      <c r="C83" t="s">
+        <v>185</v>
+      </c>
+      <c r="D83" t="s">
+        <v>33</v>
+      </c>
+      <c r="E83" t="s">
+        <v>208</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I83" t="str">
+        <f t="shared" si="1"/>
+        <v>聖</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" t="s">
+        <v>209</v>
+      </c>
+      <c r="B84" t="s">
+        <v>291</v>
+      </c>
+      <c r="C84" t="s">
+        <v>185</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E84" t="s">
         <v>135</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G45" s="4" t="s">
+      <c r="F84" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" t="str">
+        <f t="shared" si="1"/>
+        <v>冰</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" t="s">
+        <v>210</v>
+      </c>
+      <c r="B85" t="s">
+        <v>292</v>
+      </c>
+      <c r="C85" t="s">
+        <v>185</v>
+      </c>
+      <c r="D85" t="s">
+        <v>33</v>
+      </c>
+      <c r="E85" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>18</v>
+      <c r="F85" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" t="str">
+        <f t="shared" si="1"/>
+        <v>聖</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/config/Excel/NPC.xlsx
+++ b/config/Excel/NPC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B524D9AA-7D79-4445-B38B-36307351D516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3FD8AB-B9E1-45B9-A4F3-0032F947BACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="286">
   <si>
     <t>NPC識別碼</t>
   </si>
@@ -66,12 +66,6 @@
     <t>🟢</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>哥布林</t>
   </si>
   <si>
@@ -162,9 +156,6 @@
     <t>desert</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
     <t>desert_2</t>
   </si>
   <si>
@@ -222,9 +213,6 @@
     <t>🐸</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>swamp_2</t>
   </si>
   <si>
@@ -318,45 +306,30 @@
     <t>skeleton</t>
   </si>
   <si>
-    <t>35</t>
-  </si>
-  <si>
     <t>山脈怨靈</t>
   </si>
   <si>
     <t>wraith</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>腐屍獵犬</t>
   </si>
   <si>
     <t>ghoul</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>亡靈騎士</t>
   </si>
   <si>
     <t>knight</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>哀嚎女妖</t>
   </si>
   <si>
     <t>banshee</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>墓石巨像</t>
   </si>
   <si>
@@ -366,24 +339,15 @@
     <t>golem</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>血月伯爵</t>
   </si>
   <si>
     <t>vampire</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>dragon</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>god_battlefield_1</t>
   </si>
   <si>
@@ -595,9 +559,6 @@
   </si>
   <si>
     <t>💫</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
   <si>
     <t>god_sanctuary_2</t>
@@ -1341,1936 +1302,1936 @@
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="4">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4">
         <v>10</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>15</v>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>15</v>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>15</v>
+        <v>22</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4">
         <v>10</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>15</v>
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>15</v>
+      <c r="F11" s="4">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>15</v>
+        <v>34</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>15</v>
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4">
         <v>10</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>10</v>
+        <v>253</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>15</v>
+        <v>254</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F18" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="F18" s="4">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4">
         <v>10</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>10</v>
+        <v>256</v>
+      </c>
+      <c r="F20" s="4">
+        <v>1</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>10</v>
+        <v>257</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>15</v>
+      <c r="F22" s="4">
+        <v>1</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K22" s="7"/>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>10</v>
+        <v>259</v>
+      </c>
+      <c r="F23" s="4">
+        <v>0</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>10</v>
+        <v>260</v>
+      </c>
+      <c r="F24" s="4">
+        <v>1</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>15</v>
+        <v>37</v>
+      </c>
+      <c r="F25" s="4">
+        <v>0</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F26" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26" s="4">
+        <v>1</v>
+      </c>
+      <c r="G26" s="4">
         <v>10</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F27" s="4">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4">
         <v>10</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>10</v>
+        <v>41</v>
+      </c>
+      <c r="F28" s="4">
+        <v>1</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K28" s="7"/>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="F29" s="4">
+        <v>0</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>10</v>
+        <v>68</v>
+      </c>
+      <c r="F30" s="4">
+        <v>1</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>10</v>
+        <v>71</v>
+      </c>
+      <c r="F31" s="4">
+        <v>0</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>10</v>
+        <v>74</v>
+      </c>
+      <c r="F32" s="4">
+        <v>1</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>15</v>
+        <v>77</v>
+      </c>
+      <c r="F33" s="4">
+        <v>0</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>15</v>
+        <v>22</v>
+      </c>
+      <c r="F34" s="4">
+        <v>1</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>15</v>
+        <v>24</v>
+      </c>
+      <c r="F35" s="4">
+        <v>0</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>10</v>
+        <v>45</v>
+      </c>
+      <c r="F36" s="4">
+        <v>1</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>15</v>
+        <v>86</v>
+      </c>
+      <c r="F37" s="4">
+        <v>0</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F38" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F38" s="4">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4">
         <v>10</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>15</v>
+        <v>91</v>
+      </c>
+      <c r="F39" s="4">
+        <v>0</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F40" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F40" s="4">
+        <v>1</v>
+      </c>
+      <c r="G40" s="4">
         <v>10</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>10</v>
+        <v>95</v>
+      </c>
+      <c r="F41" s="4">
+        <v>0</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>15</v>
+        <v>97</v>
+      </c>
+      <c r="F42" s="4">
+        <v>1</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>10</v>
+        <v>100</v>
+      </c>
+      <c r="F43" s="4">
+        <v>0</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>15</v>
+        <v>102</v>
+      </c>
+      <c r="F44" s="4">
+        <v>1</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>10</v>
+        <v>261</v>
+      </c>
+      <c r="F45" s="4">
+        <v>0</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>115</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>15</v>
+        <v>262</v>
+      </c>
+      <c r="F46" s="4">
+        <v>1</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>10</v>
+        <v>263</v>
+      </c>
+      <c r="F47" s="4">
+        <v>0</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>15</v>
+        <v>264</v>
+      </c>
+      <c r="F48" s="4">
+        <v>1</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>10</v>
+        <v>103</v>
+      </c>
+      <c r="F49" s="4">
+        <v>0</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>115</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F50" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F50" s="4">
+        <v>1</v>
+      </c>
+      <c r="G50" s="4">
         <v>10</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>10</v>
+        <v>109</v>
+      </c>
+      <c r="F51" s="4">
+        <v>0</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>10</v>
+        <v>112</v>
+      </c>
+      <c r="F52" s="4">
+        <v>1</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>15</v>
+        <v>115</v>
+      </c>
+      <c r="F53" s="4">
+        <v>0</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="F54" s="4">
+        <v>1</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>10</v>
+        <v>120</v>
+      </c>
+      <c r="F55" s="4">
+        <v>0</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>15</v>
+        <v>123</v>
+      </c>
+      <c r="F56" s="4">
+        <v>1</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F57" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F57" s="4">
+        <v>0</v>
+      </c>
+      <c r="G57" s="4">
         <v>10</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>15</v>
+        <v>47</v>
+      </c>
+      <c r="F58" s="4">
+        <v>1</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>15</v>
+        <v>37</v>
+      </c>
+      <c r="F59" s="4">
+        <v>0</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>10</v>
+        <v>133</v>
+      </c>
+      <c r="F60" s="4">
+        <v>1</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>15</v>
+        <v>136</v>
+      </c>
+      <c r="F61" s="4">
+        <v>0</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F62" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F62" s="4">
+        <v>1</v>
+      </c>
+      <c r="G62" s="4">
         <v>10</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>15</v>
+        <v>143</v>
+      </c>
+      <c r="F63" s="4">
+        <v>0</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>15</v>
+        <v>146</v>
+      </c>
+      <c r="F64" s="4">
+        <v>1</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>10</v>
+        <v>149</v>
+      </c>
+      <c r="F65" s="4">
+        <v>0</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>10</v>
+        <v>152</v>
+      </c>
+      <c r="F66" s="4">
+        <v>1</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>15</v>
+        <v>47</v>
+      </c>
+      <c r="F67" s="4">
+        <v>0</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>15</v>
+        <v>157</v>
+      </c>
+      <c r="F68" s="4">
+        <v>1</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>15</v>
+        <v>160</v>
+      </c>
+      <c r="F69" s="4">
+        <v>0</v>
+      </c>
+      <c r="G69" s="4">
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>15</v>
+        <v>163</v>
+      </c>
+      <c r="F70" s="4">
+        <v>1</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>15</v>
+        <v>143</v>
+      </c>
+      <c r="F71" s="4">
+        <v>0</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>15</v>
+        <v>51</v>
+      </c>
+      <c r="F72" s="4">
+        <v>1</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>15</v>
+        <v>170</v>
+      </c>
+      <c r="F73" s="4">
+        <v>0</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>187</v>
+        <v>174</v>
+      </c>
+      <c r="F74" s="4">
+        <v>1</v>
+      </c>
+      <c r="G74" s="4">
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>15</v>
+        <v>176</v>
+      </c>
+      <c r="F75" s="4">
+        <v>0</v>
+      </c>
+      <c r="G75" s="4">
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>15</v>
+        <v>178</v>
+      </c>
+      <c r="F76" s="4">
+        <v>1</v>
+      </c>
+      <c r="G76" s="4">
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>10</v>
+        <v>181</v>
+      </c>
+      <c r="F77" s="4">
+        <v>0</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>15</v>
+        <v>112</v>
+      </c>
+      <c r="F78" s="4">
+        <v>1</v>
+      </c>
+      <c r="G78" s="4">
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>15</v>
+        <v>37</v>
+      </c>
+      <c r="F79" s="4">
+        <v>0</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>10</v>
+        <v>187</v>
+      </c>
+      <c r="F80" s="4">
+        <v>1</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>15</v>
+        <v>190</v>
+      </c>
+      <c r="F81" s="4">
+        <v>0</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>15</v>
+        <v>192</v>
+      </c>
+      <c r="F82" s="4">
+        <v>1</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>10</v>
+        <v>195</v>
+      </c>
+      <c r="F83" s="4">
+        <v>0</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>15</v>
+        <v>123</v>
+      </c>
+      <c r="F84" s="4">
+        <v>1</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>15</v>
+        <v>143</v>
+      </c>
+      <c r="F85" s="4">
+        <v>0</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -3322,22 +3283,22 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>10</v>
+      <c r="F2" s="8">
+        <v>1</v>
       </c>
       <c r="G2" s="8">
         <v>10</v>
@@ -3349,22 +3310,22 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>10</v>
+      <c r="F3" s="8">
+        <v>0</v>
       </c>
       <c r="G3" s="8">
         <v>1</v>
@@ -3376,22 +3337,22 @@
     </row>
     <row r="4" spans="1:15" ht="15.75">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>10</v>
+      <c r="F4" s="8">
+        <v>1</v>
       </c>
       <c r="G4" s="8">
         <v>1</v>
@@ -3404,27 +3365,27 @@
         <v>8</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>10</v>
+        <v>18</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0</v>
       </c>
       <c r="G5" s="8">
         <v>1</v>
@@ -3434,30 +3395,30 @@
         <v>地</v>
       </c>
       <c r="N5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.75">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1</v>
       </c>
       <c r="G6" s="8">
         <v>1</v>
@@ -3467,63 +3428,63 @@
         <v>火</v>
       </c>
       <c r="N6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.75">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>1</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="0"/>
+        <v>地</v>
+      </c>
+      <c r="N7" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="8">
-        <v>1</v>
-      </c>
-      <c r="I7" t="str">
-        <f t="shared" si="0"/>
-        <v>地</v>
-      </c>
-      <c r="N7" t="s">
-        <v>17</v>
-      </c>
       <c r="O7" s="5" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.75">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="F8" s="8">
+        <v>1</v>
       </c>
       <c r="G8" s="8">
         <v>10</v>
@@ -3533,30 +3494,30 @@
         <v>火</v>
       </c>
       <c r="N8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.75">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>10</v>
+      <c r="F9" s="8">
+        <v>0</v>
       </c>
       <c r="G9" s="8">
         <v>1</v>
@@ -3566,30 +3527,30 @@
         <v>地</v>
       </c>
       <c r="N9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.75">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1</v>
       </c>
       <c r="G10" s="8">
         <v>1</v>
@@ -3599,30 +3560,30 @@
         <v>暗</v>
       </c>
       <c r="N10" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>10</v>
+      <c r="F11" s="8">
+        <v>0</v>
       </c>
       <c r="G11" s="8">
         <v>1</v>
@@ -3634,22 +3595,22 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>10</v>
+        <v>34</v>
+      </c>
+      <c r="F12" s="8">
+        <v>1</v>
       </c>
       <c r="G12" s="8">
         <v>1</v>
@@ -3661,22 +3622,22 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>15</v>
+      <c r="F13" s="8">
+        <v>0</v>
       </c>
       <c r="G13" s="8">
         <v>1</v>
@@ -3688,22 +3649,22 @@
     </row>
     <row r="14" spans="1:15" ht="15">
       <c r="A14" s="2" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="F14" s="8">
+        <v>1</v>
       </c>
       <c r="G14" s="8">
         <v>10</v>
@@ -3715,25 +3676,25 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="2" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>10</v>
+        <v>253</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I15" t="str">
         <f t="shared" si="0"/>
@@ -3742,25 +3703,25 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="2" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>15</v>
+        <v>254</v>
+      </c>
+      <c r="F16" s="8">
+        <v>1</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I16" t="str">
         <f t="shared" si="0"/>
@@ -3769,25 +3730,25 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I17" t="str">
         <f t="shared" si="0"/>
@@ -3796,22 +3757,22 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>10</v>
+        <v>255</v>
+      </c>
+      <c r="F18" s="8">
+        <v>1</v>
       </c>
       <c r="G18" s="8">
         <v>10</v>
@@ -3823,25 +3784,25 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="0"/>
@@ -3850,25 +3811,25 @@
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="A20" s="2" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>10</v>
+        <v>256</v>
+      </c>
+      <c r="F20" s="8">
+        <v>1</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I20" t="str">
         <f t="shared" si="0"/>
@@ -3877,25 +3838,25 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>10</v>
+        <v>257</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I21" t="str">
         <f t="shared" si="0"/>
@@ -3904,25 +3865,25 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>15</v>
+      <c r="F22" s="8">
+        <v>1</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I22" t="str">
         <f t="shared" si="0"/>
@@ -3931,25 +3892,25 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="2" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>10</v>
+        <v>259</v>
+      </c>
+      <c r="F23" s="8">
+        <v>0</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I23" t="str">
         <f t="shared" si="0"/>
@@ -3958,25 +3919,25 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="2" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>10</v>
+        <v>260</v>
+      </c>
+      <c r="F24" s="8">
+        <v>1</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I24" t="str">
         <f t="shared" si="0"/>
@@ -3985,25 +3946,25 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="2" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>15</v>
+        <v>37</v>
+      </c>
+      <c r="F25" s="8">
+        <v>0</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="0"/>
@@ -4012,22 +3973,22 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>10</v>
+        <v>58</v>
+      </c>
+      <c r="F26" s="8">
+        <v>1</v>
       </c>
       <c r="G26" s="8">
         <v>10</v>
@@ -4039,22 +4000,22 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>10</v>
+        <v>61</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0</v>
       </c>
       <c r="G27" s="8">
         <v>10</v>
@@ -4066,25 +4027,25 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>10</v>
+        <v>41</v>
+      </c>
+      <c r="F28" s="8">
+        <v>1</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I28" t="str">
         <f t="shared" si="0"/>
@@ -4093,25 +4054,25 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="F29" s="8">
+        <v>0</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I29" t="str">
         <f t="shared" si="0"/>
@@ -4120,25 +4081,25 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>10</v>
+        <v>68</v>
+      </c>
+      <c r="F30" s="8">
+        <v>1</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I30" t="str">
         <f t="shared" si="0"/>
@@ -4147,25 +4108,25 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>10</v>
+        <v>71</v>
+      </c>
+      <c r="F31" s="8">
+        <v>0</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="0"/>
@@ -4174,25 +4135,25 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>10</v>
+        <v>74</v>
+      </c>
+      <c r="F32" s="8">
+        <v>1</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I32" t="str">
         <f t="shared" si="0"/>
@@ -4201,25 +4162,25 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>15</v>
+        <v>77</v>
+      </c>
+      <c r="F33" s="8">
+        <v>0</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I33" t="str">
         <f t="shared" si="0"/>
@@ -4228,25 +4189,25 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>15</v>
+        <v>22</v>
+      </c>
+      <c r="F34" s="8">
+        <v>1</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I34" t="str">
         <f t="shared" si="0"/>
@@ -4255,25 +4216,25 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>15</v>
+        <v>24</v>
+      </c>
+      <c r="F35" s="8">
+        <v>0</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I35" t="str">
         <f t="shared" si="0"/>
@@ -4282,25 +4243,25 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>10</v>
+        <v>45</v>
+      </c>
+      <c r="F36" s="8">
+        <v>1</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I36" t="str">
         <f t="shared" si="0"/>
@@ -4309,25 +4270,25 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>15</v>
+        <v>86</v>
+      </c>
+      <c r="F37" s="8">
+        <v>0</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I37" t="str">
         <f t="shared" si="0"/>
@@ -4336,22 +4297,22 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="2" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>10</v>
+        <v>89</v>
+      </c>
+      <c r="F38" s="8">
+        <v>1</v>
       </c>
       <c r="G38" s="8">
         <v>10</v>
@@ -4363,25 +4324,25 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="2" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>15</v>
+        <v>91</v>
+      </c>
+      <c r="F39" s="8">
+        <v>0</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I39" t="str">
         <f t="shared" si="0"/>
@@ -4390,22 +4351,22 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="2" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>10</v>
+        <v>93</v>
+      </c>
+      <c r="F40" s="8">
+        <v>1</v>
       </c>
       <c r="G40" s="8">
         <v>10</v>
@@ -4417,25 +4378,25 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>10</v>
+        <v>95</v>
+      </c>
+      <c r="F41" s="8">
+        <v>0</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I41" t="str">
         <f t="shared" si="0"/>
@@ -4444,25 +4405,25 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="2" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>15</v>
+        <v>97</v>
+      </c>
+      <c r="F42" s="8">
+        <v>1</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I42" t="str">
         <f t="shared" si="0"/>
@@ -4471,25 +4432,25 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="2" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>10</v>
+        <v>100</v>
+      </c>
+      <c r="F43" s="8">
+        <v>0</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I43" t="str">
         <f t="shared" si="0"/>
@@ -4498,25 +4459,25 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="2" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>15</v>
+        <v>102</v>
+      </c>
+      <c r="F44" s="8">
+        <v>1</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I44" t="str">
         <f t="shared" si="0"/>
@@ -4525,25 +4486,25 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="2" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>10</v>
+        <v>261</v>
+      </c>
+      <c r="F45" s="8">
+        <v>0</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I45" t="str">
         <f t="shared" si="0"/>
@@ -4552,25 +4513,25 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="2" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>15</v>
+        <v>262</v>
+      </c>
+      <c r="F46" s="8">
+        <v>1</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I46" t="str">
         <f t="shared" si="0"/>
@@ -4579,25 +4540,25 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="2" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>10</v>
+        <v>263</v>
+      </c>
+      <c r="F47" s="8">
+        <v>0</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I47" t="str">
         <f t="shared" si="0"/>
@@ -4606,25 +4567,25 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="2" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>15</v>
+        <v>264</v>
+      </c>
+      <c r="F48" s="8">
+        <v>1</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I48" t="str">
         <f t="shared" si="0"/>
@@ -4633,25 +4594,25 @@
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="2" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>10</v>
+        <v>103</v>
+      </c>
+      <c r="F49" s="8">
+        <v>0</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I49" t="str">
         <f t="shared" si="0"/>
@@ -4660,22 +4621,22 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="F50" s="8">
+        <v>1</v>
       </c>
       <c r="G50" s="8">
         <v>10</v>
@@ -4687,25 +4648,25 @@
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>10</v>
+        <v>109</v>
+      </c>
+      <c r="F51" s="8">
+        <v>0</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I51" t="str">
         <f t="shared" si="0"/>
@@ -4714,25 +4675,25 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>10</v>
+        <v>112</v>
+      </c>
+      <c r="F52" s="8">
+        <v>1</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I52" t="str">
         <f t="shared" si="0"/>
@@ -4741,25 +4702,25 @@
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>15</v>
+        <v>115</v>
+      </c>
+      <c r="F53" s="8">
+        <v>0</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I53" t="str">
         <f t="shared" si="0"/>
@@ -4768,25 +4729,25 @@
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="F54" s="8">
+        <v>1</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I54" t="str">
         <f t="shared" si="0"/>
@@ -4795,25 +4756,25 @@
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="2" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>10</v>
+        <v>120</v>
+      </c>
+      <c r="F55" s="8">
+        <v>0</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I55" t="str">
         <f t="shared" si="0"/>
@@ -4822,25 +4783,25 @@
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="2" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>15</v>
+        <v>123</v>
+      </c>
+      <c r="F56" s="8">
+        <v>1</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I56" t="str">
         <f t="shared" si="0"/>
@@ -4849,22 +4810,22 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="2" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>10</v>
+        <v>126</v>
+      </c>
+      <c r="F57" s="8">
+        <v>0</v>
       </c>
       <c r="G57" s="8">
         <v>10</v>
@@ -4876,25 +4837,25 @@
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>15</v>
+        <v>47</v>
+      </c>
+      <c r="F58" s="8">
+        <v>1</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I58" t="str">
         <f t="shared" si="0"/>
@@ -4903,25 +4864,25 @@
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="2" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>15</v>
+        <v>37</v>
+      </c>
+      <c r="F59" s="8">
+        <v>0</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I59" t="str">
         <f t="shared" si="0"/>
@@ -4930,25 +4891,25 @@
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="2" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>10</v>
+        <v>133</v>
+      </c>
+      <c r="F60" s="8">
+        <v>1</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I60" t="str">
         <f t="shared" si="0"/>
@@ -4957,25 +4918,25 @@
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="2" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>15</v>
+        <v>136</v>
+      </c>
+      <c r="F61" s="8">
+        <v>0</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I61" t="str">
         <f t="shared" si="0"/>
@@ -4984,22 +4945,22 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="2" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>10</v>
+        <v>140</v>
+      </c>
+      <c r="F62" s="8">
+        <v>1</v>
       </c>
       <c r="G62" s="8">
         <v>10</v>
@@ -5011,25 +4972,25 @@
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="2" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>15</v>
+        <v>143</v>
+      </c>
+      <c r="F63" s="8">
+        <v>0</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I63" t="str">
         <f t="shared" si="0"/>
@@ -5038,25 +4999,25 @@
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="2" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>15</v>
+        <v>146</v>
+      </c>
+      <c r="F64" s="8">
+        <v>1</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I64" t="str">
         <f t="shared" si="0"/>
@@ -5065,25 +5026,25 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="2" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>10</v>
+        <v>149</v>
+      </c>
+      <c r="F65" s="8">
+        <v>0</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I65" t="str">
         <f t="shared" si="0"/>
@@ -5092,25 +5053,25 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="2" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>10</v>
+        <v>152</v>
+      </c>
+      <c r="F66" s="8">
+        <v>1</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I66" t="str">
         <f t="shared" si="0"/>
@@ -5119,25 +5080,25 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>15</v>
+        <v>47</v>
+      </c>
+      <c r="F67" s="8">
+        <v>0</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I67" t="str">
         <f t="shared" ref="I67:I85" si="1">VLOOKUP(D67,$N$4:$O$10,2,0)</f>
@@ -5146,25 +5107,25 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="2" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D68" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>15</v>
+        <v>157</v>
+      </c>
+      <c r="F68" s="8">
+        <v>1</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I68" t="str">
         <f t="shared" si="1"/>
@@ -5173,22 +5134,22 @@
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="2" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>15</v>
+        <v>160</v>
+      </c>
+      <c r="F69" s="8">
+        <v>0</v>
       </c>
       <c r="G69" s="8">
         <v>10</v>
@@ -5200,25 +5161,25 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="2" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>15</v>
+        <v>163</v>
+      </c>
+      <c r="F70" s="8">
+        <v>1</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I70" t="str">
         <f t="shared" si="1"/>
@@ -5227,25 +5188,25 @@
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="2" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>15</v>
+        <v>143</v>
+      </c>
+      <c r="F71" s="8">
+        <v>0</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I71" t="str">
         <f t="shared" si="1"/>
@@ -5254,25 +5215,25 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="2" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>15</v>
+        <v>51</v>
+      </c>
+      <c r="F72" s="8">
+        <v>1</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I72" t="str">
         <f t="shared" si="1"/>
@@ -5281,25 +5242,25 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="2" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>15</v>
+        <v>170</v>
+      </c>
+      <c r="F73" s="8">
+        <v>0</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I73" t="str">
         <f t="shared" si="1"/>
@@ -5308,22 +5269,22 @@
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="2" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>15</v>
+        <v>174</v>
+      </c>
+      <c r="F74" s="8">
+        <v>1</v>
       </c>
       <c r="G74" s="8">
         <v>10</v>
@@ -5335,22 +5296,22 @@
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="2" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>15</v>
+        <v>176</v>
+      </c>
+      <c r="F75" s="8">
+        <v>0</v>
       </c>
       <c r="G75" s="8">
         <v>5</v>
@@ -5362,22 +5323,22 @@
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>15</v>
+        <v>178</v>
+      </c>
+      <c r="F76" s="8">
+        <v>1</v>
       </c>
       <c r="G76" s="8">
         <v>5</v>
@@ -5389,25 +5350,25 @@
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="2" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>10</v>
+        <v>181</v>
+      </c>
+      <c r="F77" s="8">
+        <v>0</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I77" t="str">
         <f t="shared" si="1"/>
@@ -5416,22 +5377,22 @@
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="2" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>10</v>
+        <v>112</v>
+      </c>
+      <c r="F78" s="8">
+        <v>1</v>
       </c>
       <c r="G78" s="8">
         <v>5</v>
@@ -5443,25 +5404,25 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>15</v>
+        <v>37</v>
+      </c>
+      <c r="F79" s="8">
+        <v>0</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I79" t="str">
         <f t="shared" si="1"/>
@@ -5470,25 +5431,25 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="2" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>10</v>
+        <v>187</v>
+      </c>
+      <c r="F80" s="8">
+        <v>1</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I80" t="str">
         <f t="shared" si="1"/>
@@ -5497,25 +5458,25 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="2" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>15</v>
+        <v>190</v>
+      </c>
+      <c r="F81" s="8">
+        <v>0</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I81" t="str">
         <f t="shared" si="1"/>
@@ -5524,25 +5485,25 @@
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="B82" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="C82" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D82" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E82" t="s">
-        <v>205</v>
-      </c>
-      <c r="F82" s="9" t="s">
-        <v>15</v>
+        <v>192</v>
+      </c>
+      <c r="F82" s="8">
+        <v>1</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I82" t="str">
         <f t="shared" si="1"/>
@@ -5551,25 +5512,25 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="B83" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C83" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D83" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E83" t="s">
-        <v>208</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>10</v>
+        <v>195</v>
+      </c>
+      <c r="F83" s="8">
+        <v>0</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I83" t="str">
         <f t="shared" si="1"/>
@@ -5578,25 +5539,25 @@
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="B84" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C84" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="E84" t="s">
-        <v>135</v>
-      </c>
-      <c r="F84" s="9" t="s">
-        <v>15</v>
+        <v>123</v>
+      </c>
+      <c r="F84" s="8">
+        <v>1</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I84" t="str">
         <f t="shared" si="1"/>
@@ -5605,25 +5566,25 @@
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B85" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="C85" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D85" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E85" t="s">
-        <v>155</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>15</v>
+        <v>143</v>
+      </c>
+      <c r="F85" s="8">
+        <v>0</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I85" t="str">
         <f t="shared" si="1"/>

--- a/config/Excel/NPC.xlsx
+++ b/config/Excel/NPC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3FD8AB-B9E1-45B9-A4F3-0032F947BACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A366EC9C-ADBF-437F-9241-0CCD738E94B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="286">
   <si>
     <t>NPC識別碼</t>
   </si>
@@ -672,10 +672,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>巨魔像</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>寒霜狼</t>
   </si>
   <si>
@@ -914,6 +910,10 @@
   </si>
   <si>
     <t>ice</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨靈像</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1495,7 +1495,7 @@
         <v>39</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>29</v>
@@ -1578,13 +1578,13 @@
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>36</v>
@@ -1601,19 +1601,19 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F15" s="4">
         <v>0</v>
@@ -1624,19 +1624,19 @@
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F16" s="4">
         <v>1</v>
@@ -1647,13 +1647,13 @@
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>36</v>
@@ -1670,19 +1670,19 @@
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F18" s="4">
         <v>1</v>
@@ -1693,13 +1693,13 @@
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>15</v>
@@ -1716,19 +1716,19 @@
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F20" s="4">
         <v>1</v>
@@ -1739,19 +1739,19 @@
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F21" s="4">
         <v>0</v>
@@ -1762,19 +1762,19 @@
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F22" s="4">
         <v>1</v>
@@ -1786,19 +1786,19 @@
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F23" s="4">
         <v>0</v>
@@ -1809,19 +1809,19 @@
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F24" s="4">
         <v>1</v>
@@ -1832,13 +1832,13 @@
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1">
       <c r="A25" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>15</v>
@@ -1980,7 +1980,7 @@
         <v>57</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>71</v>
@@ -2132,7 +2132,7 @@
     </row>
     <row r="38" spans="1:7" ht="15" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>87</v>
@@ -2155,7 +2155,7 @@
     </row>
     <row r="39" spans="1:7" ht="15" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>90</v>
@@ -2164,7 +2164,7 @@
         <v>88</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>11</v>
+        <v>283</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>91</v>
@@ -2178,7 +2178,7 @@
     </row>
     <row r="40" spans="1:7" ht="15" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>92</v>
@@ -2201,7 +2201,7 @@
     </row>
     <row r="41" spans="1:7" ht="15" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>94</v>
@@ -2224,7 +2224,7 @@
     </row>
     <row r="42" spans="1:7" ht="15" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>96</v>
@@ -2247,7 +2247,7 @@
     </row>
     <row r="43" spans="1:7" ht="15" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>98</v>
@@ -2256,7 +2256,7 @@
         <v>88</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>100</v>
@@ -2270,7 +2270,7 @@
     </row>
     <row r="44" spans="1:7" ht="15" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>101</v>
@@ -2279,7 +2279,7 @@
         <v>88</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>102</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="45" spans="1:7" ht="15" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>88</v>
@@ -2305,7 +2305,7 @@
         <v>8</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F45" s="4">
         <v>0</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="46" spans="1:7" ht="15" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>88</v>
@@ -2328,7 +2328,7 @@
         <v>11</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F46" s="4">
         <v>1</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="47" spans="1:7" ht="15" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>88</v>
@@ -2351,7 +2351,7 @@
         <v>8</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F47" s="4">
         <v>0</v>
@@ -2362,10 +2362,10 @@
     </row>
     <row r="48" spans="1:7" ht="15" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>88</v>
@@ -2374,7 +2374,7 @@
         <v>11</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F48" s="4">
         <v>1</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="49" spans="1:7" ht="15" customHeight="1">
       <c r="A49" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>88</v>
@@ -2601,7 +2601,7 @@
         <v>106</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>47</v>
@@ -2831,7 +2831,7 @@
         <v>139</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>157</v>
@@ -3015,7 +3015,7 @@
         <v>173</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>31</v>
+        <v>279</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>178</v>
@@ -3038,7 +3038,7 @@
         <v>173</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>181</v>
@@ -3101,13 +3101,13 @@
         <v>186</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>173</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>187</v>
@@ -3115,8 +3115,8 @@
       <c r="F80" s="4">
         <v>1</v>
       </c>
-      <c r="G80" s="4" t="s">
-        <v>13</v>
+      <c r="G80" s="4">
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15" customHeight="1">
@@ -3130,7 +3130,7 @@
         <v>173</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>36</v>
+        <v>279</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>190</v>
@@ -3319,7 +3319,7 @@
         <v>39</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>12</v>
@@ -3406,13 +3406,13 @@
         <v>44</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>20</v>
@@ -3478,7 +3478,7 @@
         <v>39</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>24</v>
@@ -3563,7 +3563,7 @@
         <v>99</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -3604,7 +3604,7 @@
         <v>39</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>34</v>
@@ -3631,7 +3631,7 @@
         <v>39</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>37</v>
@@ -3649,13 +3649,13 @@
     </row>
     <row r="14" spans="1:15" ht="15">
       <c r="A14" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>36</v>
@@ -3676,19 +3676,19 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F15" s="8">
         <v>0</v>
@@ -3703,19 +3703,19 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F16" s="8">
         <v>1</v>
@@ -3730,13 +3730,13 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>36</v>
@@ -3757,19 +3757,19 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F18" s="8">
         <v>1</v>
@@ -3784,13 +3784,13 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>15</v>
@@ -3811,19 +3811,19 @@
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="A20" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F20" s="8">
         <v>1</v>
@@ -3838,19 +3838,19 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F21" s="8">
         <v>0</v>
@@ -3865,19 +3865,19 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F22" s="8">
         <v>1</v>
@@ -3892,19 +3892,19 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F23" s="8">
         <v>0</v>
@@ -3919,19 +3919,19 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F24" s="8">
         <v>1</v>
@@ -3946,13 +3946,13 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>15</v>
@@ -4297,7 +4297,7 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>87</v>
@@ -4324,7 +4324,7 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>90</v>
@@ -4351,7 +4351,7 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>92</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>94</v>
@@ -4405,7 +4405,7 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>96</v>
@@ -4432,7 +4432,7 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>98</v>
@@ -4459,7 +4459,7 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>101</v>
@@ -4468,7 +4468,7 @@
         <v>88</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>102</v>
@@ -4486,10 +4486,10 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>88</v>
@@ -4498,7 +4498,7 @@
         <v>8</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F45" s="8">
         <v>0</v>
@@ -4513,10 +4513,10 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>88</v>
@@ -4525,7 +4525,7 @@
         <v>11</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F46" s="8">
         <v>1</v>
@@ -4540,10 +4540,10 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>88</v>
@@ -4552,7 +4552,7 @@
         <v>8</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F47" s="8">
         <v>0</v>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>88</v>
@@ -4579,7 +4579,7 @@
         <v>11</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F48" s="8">
         <v>1</v>
@@ -4594,10 +4594,10 @@
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>88</v>
@@ -4711,7 +4711,7 @@
         <v>106</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>115</v>
@@ -4765,7 +4765,7 @@
         <v>106</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>120</v>
@@ -4819,7 +4819,7 @@
         <v>106</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>126</v>
@@ -4846,7 +4846,7 @@
         <v>106</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>47</v>
@@ -4873,7 +4873,7 @@
         <v>106</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>37</v>
@@ -4900,7 +4900,7 @@
         <v>106</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>133</v>
@@ -4927,7 +4927,7 @@
         <v>106</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>136</v>
@@ -5299,7 +5299,7 @@
         <v>175</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>173</v>
@@ -5326,7 +5326,7 @@
         <v>177</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>173</v>
@@ -5359,7 +5359,7 @@
         <v>173</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>181</v>
@@ -5434,7 +5434,7 @@
         <v>186</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>173</v>
@@ -5488,7 +5488,7 @@
         <v>191</v>
       </c>
       <c r="B82" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C82" t="s">
         <v>173</v>
@@ -5542,13 +5542,13 @@
         <v>196</v>
       </c>
       <c r="B84" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C84" t="s">
         <v>173</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E84" t="s">
         <v>123</v>
@@ -5569,7 +5569,7 @@
         <v>197</v>
       </c>
       <c r="B85" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C85" t="s">
         <v>173</v>

--- a/config/Excel/NPC.xlsx
+++ b/config/Excel/NPC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A366EC9C-ADBF-437F-9241-0CCD738E94B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DD928C-7DAC-4007-B698-E7E9F2823854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="287">
   <si>
     <t>NPC識別碼</t>
   </si>
@@ -914,6 +914,10 @@
   </si>
   <si>
     <t>巨靈像</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>god_chaos</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2828,7 +2832,7 @@
         <v>156</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>139</v>
+        <v>286</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>36</v>
